--- a/output/yearly_surface_area_iteration_48_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_48_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.8449764555536</v>
+        <v>10.84497619613818</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907237167984</v>
+        <v>37.78907146775273</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.727516106575892</v>
+        <v>6.319509972236719</v>
       </c>
       <c r="C2" t="n">
-        <v>5.952336330848412</v>
+        <v>5.322054304721958</v>
       </c>
       <c r="D2" t="n">
-        <v>22.45551523923729</v>
+        <v>26.31476546463151</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.42878706704438</v>
+        <v>19.69385894719102</v>
       </c>
       <c r="C3" t="n">
-        <v>21.71625921793945</v>
+        <v>33.241977265797</v>
       </c>
       <c r="D3" t="n">
-        <v>70.96563280148068</v>
+        <v>66.83738370512286</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.78666731520473</v>
+        <v>40.85346721682252</v>
       </c>
       <c r="C4" t="n">
-        <v>80.99222210495337</v>
+        <v>83.00873188947631</v>
       </c>
       <c r="D4" t="n">
-        <v>86.79925977557325</v>
+        <v>74.44494666533139</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.89041377668541</v>
+        <v>52.40078371417351</v>
       </c>
       <c r="C5" t="n">
-        <v>143.0406405087603</v>
+        <v>126.3018421513522</v>
       </c>
       <c r="D5" t="n">
-        <v>61.04016351154545</v>
+        <v>53.4070751110265</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>43.55229165579701</v>
+        <v>51.15985461600555</v>
       </c>
       <c r="C6" t="n">
-        <v>144.6241995557104</v>
+        <v>163.5022261606723</v>
       </c>
       <c r="D6" t="n">
-        <v>43.06927178530758</v>
+        <v>41.74096714146165</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.48228446915921</v>
+        <v>38.32743037379547</v>
       </c>
       <c r="C7" t="n">
-        <v>111.9280740134746</v>
+        <v>145.8238952503</v>
       </c>
       <c r="D7" t="n">
-        <v>38.38731698375453</v>
+        <v>37.96811071404115</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.85522542358599</v>
+        <v>19.69385894719101</v>
       </c>
       <c r="C8" t="n">
-        <v>68.42781498600267</v>
+        <v>83.86579763528377</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>35.9663271450819</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.876561831172157</v>
+        <v>8.764061755811273</v>
       </c>
       <c r="C9" t="n">
-        <v>38.38437174064178</v>
+        <v>42.15624642035802</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>34.87658719336794</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,10 +906,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>29.31989518733098</v>
+        <v>28.78680618392497</v>
       </c>
       <c r="D11" t="n">
         <v>36.07235589714055</v>
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.55471281509523</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>24.97566159603886</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>32.5203927031756</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>18.59921025695582</v>
+        <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -993,10 +993,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.682066915300113</v>
+        <v>7.657164701394977</v>
       </c>
       <c r="C21" t="n">
-        <v>94.10531971242638</v>
+        <v>92.8431220044141</v>
       </c>
       <c r="D21" t="n">
-        <v>8.642325279712628</v>
+        <v>7.657164701394977</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.140831890063798</v>
+        <v>7.152032025438014</v>
       </c>
       <c r="C2" t="n">
-        <v>9.24315463548372</v>
+        <v>15.6667298643706</v>
       </c>
       <c r="D2" t="n">
-        <v>21.69269727303752</v>
+        <v>24.05870924027233</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.15880644837651</v>
+        <v>20.17491532227195</v>
       </c>
       <c r="C3" t="n">
-        <v>22.29549036344507</v>
+        <v>26.81152980298039</v>
       </c>
       <c r="D3" t="n">
-        <v>71.81484456565418</v>
+        <v>70.73492209098269</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.93981995706723</v>
+        <v>39.0283982346277</v>
       </c>
       <c r="C4" t="n">
-        <v>66.97875537453439</v>
+        <v>82.8555792476138</v>
       </c>
       <c r="D4" t="n">
-        <v>100.0980141773005</v>
+        <v>86.722683454642</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.16101629015904</v>
+        <v>55.93507544946203</v>
       </c>
       <c r="C5" t="n">
-        <v>145.9122525436822</v>
+        <v>137.1746979758856</v>
       </c>
       <c r="D5" t="n">
-        <v>74.8582624488193</v>
+        <v>65.55620295108078</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.20010627187966</v>
+        <v>59.61270234957058</v>
       </c>
       <c r="C6" t="n">
-        <v>181.5349679922778</v>
+        <v>180.8104381865436</v>
       </c>
       <c r="D6" t="n">
-        <v>51.24035792775378</v>
+        <v>47.37619896383834</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>40.12402867256714</v>
+        <v>48.32849423695774</v>
       </c>
       <c r="C7" t="n">
-        <v>157.3820109723977</v>
+        <v>185.3490578232766</v>
       </c>
       <c r="D7" t="n">
-        <v>41.3816474817073</v>
+        <v>41.08221443191203</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>23.78283813537898</v>
+        <v>29.45733986592554</v>
       </c>
       <c r="C8" t="n">
-        <v>104.5610392408065</v>
+        <v>132.0990623449296</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>37.55184968744049</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.42656152972862</v>
+        <v>13.42343636016663</v>
       </c>
       <c r="C9" t="n">
-        <v>59.90624491314035</v>
+        <v>69.89061906533041</v>
       </c>
       <c r="D9" t="n">
-        <v>35.16718451382499</v>
+        <v>35.05624702324509</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.405903770210439</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>37.29659528433633</v>
+        <v>39.14718970684157</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.34073287329842</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.83745615391831</v>
+        <v>27.57729301229291</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>24.89024954576939</v>
       </c>
       <c r="D14" t="n">
-        <v>31.34327720578367</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.83915760741954</v>
+        <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1307,7 +1307,7 @@
         <v>18.41660518396592</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.85865006198225</v>
+        <v>7.827696917858287</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1624508057693</v>
+        <v>100.7815978174254</v>
       </c>
       <c r="D21" t="n">
-        <v>9.823312577477813</v>
+        <v>8.806159032590573</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.290859362364314</v>
+        <v>8.200538573573606</v>
       </c>
       <c r="C2" t="n">
-        <v>12.09414996861646</v>
+        <v>15.32508166329271</v>
       </c>
       <c r="D2" t="n">
-        <v>23.61888626876977</v>
+        <v>19.46805697521425</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.36988220478957</v>
+        <v>21.29901644363455</v>
       </c>
       <c r="C3" t="n">
-        <v>28.40686982238146</v>
+        <v>41.61628518302229</v>
       </c>
       <c r="D3" t="n">
-        <v>71.61358628628358</v>
+        <v>72.15354752361934</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.2889212291516</v>
+        <v>37.70107533848601</v>
       </c>
       <c r="C4" t="n">
-        <v>61.68222651012285</v>
+        <v>74.90440459091889</v>
       </c>
       <c r="D4" t="n">
-        <v>108.5596976402038</v>
+        <v>98.06874167262238</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.70726892434777</v>
+        <v>56.47503668679778</v>
       </c>
       <c r="C5" t="n">
-        <v>134.4012607113884</v>
+        <v>141.9361743414826</v>
       </c>
       <c r="D5" t="n">
-        <v>89.51084693470295</v>
+        <v>76.52723354603889</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>57.27810630887167</v>
+        <v>66.25422556880025</v>
       </c>
       <c r="C6" t="n">
-        <v>201.4192859940926</v>
+        <v>196.6293389450724</v>
       </c>
       <c r="D6" t="n">
-        <v>59.65295400544471</v>
+        <v>54.82275530055039</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.10702016642545</v>
+        <v>57.01205268102077</v>
       </c>
       <c r="C7" t="n">
-        <v>202.5964014914845</v>
+        <v>215.4121360227224</v>
       </c>
       <c r="D7" t="n">
-        <v>45.6934833987593</v>
+        <v>43.95677170994669</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>31.62700229231099</v>
+        <v>38.30288668118931</v>
       </c>
       <c r="C8" t="n">
-        <v>147.2866993296277</v>
+        <v>177.661973299024</v>
       </c>
       <c r="D8" t="n">
-        <v>39.72151211382594</v>
+        <v>39.63806355896497</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.41874860582365</v>
+        <v>19.63593583264045</v>
       </c>
       <c r="C9" t="n">
-        <v>88.74999246391164</v>
+        <v>108.1640533153923</v>
       </c>
       <c r="D9" t="n">
-        <v>36.72030938194344</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
-        <v>51.53193699591508</v>
+        <v>55.94489292650449</v>
       </c>
       <c r="D10" t="n">
-        <v>36.01541453029424</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>36.78314123501524</v>
+        <v>37.31623023842126</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1548,7 +1548,7 @@
         <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>35.79943003535993</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>30.43908757017236</v>
+        <v>29.65859814529614</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
-        <v>31.65056423721292</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.72531593145592</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>19.36104647545135</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1632,7 +1632,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.019474181384734</v>
+        <v>7.98160507926269</v>
       </c>
       <c r="C21" t="n">
-        <v>110.2677699940401</v>
+        <v>107.7516685700463</v>
       </c>
       <c r="D21" t="n">
-        <v>11.02677699940401</v>
+        <v>9.977006349078362</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.499570712741384</v>
+        <v>7.585964510715104</v>
       </c>
       <c r="C2" t="n">
-        <v>8.320311793491719</v>
+        <v>10.7884255219682</v>
       </c>
       <c r="D2" t="n">
-        <v>19.58193970890688</v>
+        <v>16.2665777116654</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.77302065833651</v>
+        <v>25.41744806294992</v>
       </c>
       <c r="C3" t="n">
-        <v>43.83503499462009</v>
+        <v>59.74916528046088</v>
       </c>
       <c r="D3" t="n">
-        <v>78.13729978100365</v>
+        <v>77.39117152577607</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.35127005613788</v>
+        <v>27.13354304997335</v>
       </c>
       <c r="C4" t="n">
-        <v>100.8382519463026</v>
+        <v>110.3975293425538</v>
       </c>
       <c r="D4" t="n">
-        <v>103.0334398129985</v>
+        <v>91.5214662330004</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.25041208450773</v>
+        <v>37.3064127613788</v>
       </c>
       <c r="C5" t="n">
-        <v>120.3377248480528</v>
+        <v>117.490656505737</v>
       </c>
       <c r="D5" t="n">
-        <v>59.69026041820608</v>
+        <v>53.30890034060182</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.47050349670826</v>
+        <v>35.38120551335081</v>
       </c>
       <c r="C6" t="n">
-        <v>133.4342392227053</v>
+        <v>141.8870869562703</v>
       </c>
       <c r="D6" t="n">
-        <v>30.06798693796707</v>
+        <v>28.94094057349173</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.9603134856694</v>
+        <v>25.3919226226395</v>
       </c>
       <c r="C7" t="n">
-        <v>103.5439486192068</v>
+        <v>124.9234683745896</v>
       </c>
       <c r="D7" t="n">
-        <v>27.90716024091983</v>
+        <v>27.84727363096077</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.34900346109313</v>
+        <v>13.60211444233956</v>
       </c>
       <c r="C8" t="n">
-        <v>65.42366701100744</v>
+        <v>79.69336989223483</v>
       </c>
       <c r="D8" t="n">
-        <v>27.03733177495716</v>
+        <v>26.53664044579129</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="C9" t="n">
-        <v>39.2718716652809</v>
+        <v>42.71093387325747</v>
       </c>
       <c r="D9" t="n">
-        <v>27.40156017323271</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>28.75539025738908</v>
+        <v>29.18245050873644</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>28.89774367450487</v>
       </c>
     </row>
     <row r="11">
@@ -1845,7 +1845,7 @@
         <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.60910984945629</v>
+        <v>28.07602084605028</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>26.68684784454105</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.97566159603886</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>20.58823110575986</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>23.96838845148163</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.57528845915541</v>
+        <v>21.85861263505523</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.11931555602838</v>
+        <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>20.25247339090745</v>
       </c>
     </row>
     <row r="17">
@@ -1929,7 +1929,7 @@
         <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>73.97468951499715</v>
+        <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.628940425523711</v>
+        <v>4.710425484976196</v>
       </c>
       <c r="C2" t="n">
-        <v>3.698243601897735</v>
+        <v>5.324017800130453</v>
       </c>
       <c r="D2" t="n">
-        <v>13.62174939642449</v>
+        <v>11.56989669454866</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.36345193921635</v>
+        <v>26.34029090494192</v>
       </c>
       <c r="C3" t="n">
-        <v>38.85266539556753</v>
+        <v>51.97372346282614</v>
       </c>
       <c r="D3" t="n">
-        <v>77.07210352189585</v>
+        <v>74.21030896401639</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.46385224695678</v>
+        <v>36.14402347955058</v>
       </c>
       <c r="C4" t="n">
-        <v>108.6617994014455</v>
+        <v>132.6174251327719</v>
       </c>
       <c r="D4" t="n">
-        <v>115.2984138821539</v>
+        <v>106.2879334525767</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.88287859022093</v>
+        <v>40.98796665230434</v>
       </c>
       <c r="C5" t="n">
-        <v>152.1218067730433</v>
+        <v>157.987749305918</v>
       </c>
       <c r="D5" t="n">
-        <v>76.28179661997717</v>
+        <v>66.83247496660162</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.06548366321083</v>
+        <v>41.33845058272045</v>
       </c>
       <c r="C6" t="n">
-        <v>163.6632327841688</v>
+        <v>165.756318889623</v>
       </c>
       <c r="D6" t="n">
-        <v>37.07177506006381</v>
+        <v>34.49566908412018</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.58292145661112</v>
+        <v>23.77498415374501</v>
       </c>
       <c r="C7" t="n">
-        <v>136.7211305365236</v>
+        <v>157.8012172421111</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>30.12296480940488</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.429686699290613</v>
+        <v>11.01520924164921</v>
       </c>
       <c r="C8" t="n">
-        <v>88.53891670749859</v>
+        <v>104.8948334602505</v>
       </c>
       <c r="D8" t="n">
-        <v>27.78836876870596</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>44.04218376021615</v>
+        <v>46.59374604355361</v>
       </c>
       <c r="D9" t="n">
         <v>28.39999758845172</v>
@@ -2139,10 +2139,10 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>30.03657101143117</v>
+        <v>29.60951076008381</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
+        <v>28.78680618392497</v>
+      </c>
+      <c r="D11" t="n">
         <v>29.31989518733098</v>
-      </c>
-      <c r="D11" t="n">
-        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.82875929330033</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>18.12993485432585</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>13.97517856995334</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.20021977840412</v>
       </c>
     </row>
     <row r="16">
@@ -2226,7 +2226,7 @@
         <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>64.39381366925254</v>
+        <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.147884050442774</v>
+        <v>4.671155576806324</v>
       </c>
       <c r="C2" t="n">
-        <v>7.028331814702915</v>
+        <v>7.024404823885929</v>
       </c>
       <c r="D2" t="n">
-        <v>21.52089142479433</v>
+        <v>10.19250466549039</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.52343575727957</v>
+        <v>21.18611545764617</v>
       </c>
       <c r="C3" t="n">
-        <v>25.81996462169111</v>
+        <v>36.09395434663399</v>
       </c>
       <c r="D3" t="n">
-        <v>70.67110849020665</v>
+        <v>66.99446333780234</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.70031457496002</v>
+        <v>42.72958707963818</v>
       </c>
       <c r="C4" t="n">
-        <v>102.6505582083422</v>
+        <v>131.034847833526</v>
       </c>
       <c r="D4" t="n">
-        <v>125.6745053683384</v>
+        <v>117.1872964651248</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.36241343824987</v>
+        <v>46.90299657039137</v>
       </c>
       <c r="C5" t="n">
-        <v>177.1563732313369</v>
+        <v>198.4848421060989</v>
       </c>
       <c r="D5" t="n">
-        <v>96.28490609400595</v>
+        <v>85.92746781420209</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.66046382971341</v>
+        <v>47.45670227558657</v>
       </c>
       <c r="C6" t="n">
-        <v>199.9702263826244</v>
+        <v>206.1287297313646</v>
       </c>
       <c r="D6" t="n">
-        <v>49.22777513404782</v>
+        <v>44.84034464376883</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.86534600026472</v>
+        <v>33.59638818703009</v>
       </c>
       <c r="C7" t="n">
-        <v>184.0315524041773</v>
+        <v>194.2721627071758</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.60211444233956</v>
+        <v>16.02212253330794</v>
       </c>
       <c r="C8" t="n">
-        <v>130.263194137988</v>
+        <v>150.8749871886498</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>29.12354564648163</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.323436963053704</v>
+        <v>6.767186925373262</v>
       </c>
       <c r="C9" t="n">
-        <v>71.88749389576842</v>
+        <v>81.09530561389926</v>
       </c>
       <c r="D9" t="n">
-        <v>29.28749751309084</v>
+        <v>28.95468504135117</v>
       </c>
     </row>
     <row r="10">
@@ -2450,10 +2450,10 @@
         <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>40.57072387799944</v>
+        <v>40.9977841293468</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>30.17892442854695</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>30.03068052520567</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2475,10 +2475,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.47158305540374</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.28621266575034</v>
+        <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>19.35908298004286</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2520,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>15.0501923061036</v>
+        <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>16.84188186635403</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>34.3032465340878</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.502474898125119</v>
+        <v>2.855904071653971</v>
       </c>
       <c r="C2" t="n">
-        <v>3.28394607070558</v>
+        <v>3.423354244708628</v>
       </c>
       <c r="D2" t="n">
-        <v>15.05117405380785</v>
+        <v>7.132397071353077</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.85584731839174</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="C3" t="n">
-        <v>28.16634163484099</v>
+        <v>34.7980473770282</v>
       </c>
       <c r="D3" t="n">
-        <v>72.92912820997431</v>
+        <v>63.82341825308514</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.860961345558</v>
+        <v>46.99233561147783</v>
       </c>
       <c r="C4" t="n">
-        <v>99.75342073310991</v>
+        <v>129.4522705342802</v>
       </c>
       <c r="D4" t="n">
-        <v>133.3831883420844</v>
+        <v>124.6024368753009</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.05592822807562</v>
+        <v>49.30827844579606</v>
       </c>
       <c r="C5" t="n">
-        <v>208.5232123820226</v>
+        <v>239.9145952253143</v>
       </c>
       <c r="D5" t="n">
-        <v>101.6845184673634</v>
+        <v>91.35162388016572</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.85793398698726</v>
+        <v>39.24536447726626</v>
       </c>
       <c r="C6" t="n">
-        <v>238.1287961512894</v>
+        <v>243.8445312854143</v>
       </c>
       <c r="D6" t="n">
-        <v>48.46299367243955</v>
+        <v>44.03531152628644</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.982991493858314</v>
+        <v>10.59992996275281</v>
       </c>
       <c r="C7" t="n">
-        <v>184.0315524041773</v>
+        <v>200.97946302259</v>
       </c>
       <c r="D7" t="n">
-        <v>33.83593462686632</v>
+        <v>32.99752208743954</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.339324852770902</v>
+        <v>4.673119072214817</v>
       </c>
       <c r="C8" t="n">
-        <v>92.54444734082557</v>
+        <v>102.641722479004</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>30.87596529856218</v>
       </c>
     </row>
     <row r="9">
@@ -2747,10 +2747,10 @@
         <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>30.95155987178918</v>
+        <v>31.28437234352885</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.76596849795754</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>23.48831382410494</v>
+        <v>23.06125357275758</v>
       </c>
     </row>
     <row r="11">
@@ -2772,10 +2772,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.62156946997525</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.26832022289564</v>
+        <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -2817,10 +2817,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>12.59876828859932</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29.42788743479814</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.873575530330414</v>
+        <v>3.279037332184346</v>
       </c>
       <c r="C2" t="n">
-        <v>5.899321954819084</v>
+        <v>2.615375884113503</v>
       </c>
       <c r="D2" t="n">
-        <v>17.6508419746534</v>
+        <v>14.12145897788612</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.42187377538564</v>
+        <v>15.61960597456675</v>
       </c>
       <c r="C3" t="n">
-        <v>20.35653864755761</v>
+        <v>24.27371198750239</v>
       </c>
       <c r="D3" t="n">
-        <v>69.04140730115694</v>
+        <v>56.02834148136547</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.98934931063608</v>
+        <v>44.03138453546944</v>
       </c>
       <c r="C4" t="n">
-        <v>86.14836104765762</v>
+        <v>109.1723082076538</v>
       </c>
       <c r="D4" t="n">
-        <v>137.9650048778043</v>
+        <v>127.1549809063426</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.79977419272522</v>
+        <v>58.07037670619884</v>
       </c>
       <c r="C5" t="n">
-        <v>198.8039101099791</v>
+        <v>241.1172361630167</v>
       </c>
       <c r="D5" t="n">
-        <v>120.8776860853885</v>
+        <v>109.9066554904305</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.19631814978292</v>
+        <v>49.22777513404782</v>
       </c>
       <c r="C6" t="n">
-        <v>281.1578162807228</v>
+        <v>304.3830217200896</v>
       </c>
       <c r="D6" t="n">
-        <v>63.71837124873075</v>
+        <v>58.08313942635406</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.46314823669301</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="C7" t="n">
-        <v>252.4819475873777</v>
+        <v>266.6750741476738</v>
       </c>
       <c r="D7" t="n">
-        <v>38.68675003354981</v>
+        <v>36.47094546506476</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>154.6301721573939</v>
+        <v>165.3950357344601</v>
       </c>
       <c r="D8" t="n">
-        <v>32.87873061522568</v>
+        <v>32.46148784092078</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.440624792757569</v>
       </c>
       <c r="C9" t="n">
-        <v>60.68280734719958</v>
+        <v>64.12186955517615</v>
       </c>
       <c r="D9" t="n">
-        <v>32.50468473990763</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.34243432679967</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.3553926689373453</v>
       </c>
       <c r="C11" t="n">
-        <v>23.63361248433346</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>23.81130881880213</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.7912318963607</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
-        <v>21.47965802121596</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>14.82929907264807</v>
+      </c>
+      <c r="D13" t="n">
         <v>15.34962535589888</v>
-      </c>
-      <c r="D13" t="n">
-        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.52062938288707</v>
+        <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
         <v>8.266315669758143</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.99988649347554</v>
+        <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.198133109808608</v>
+        <v>2.351285751671111</v>
       </c>
       <c r="C2" t="n">
-        <v>3.087596529856219</v>
+        <v>2.090140862341459</v>
       </c>
       <c r="D2" t="n">
-        <v>13.71010668980671</v>
+        <v>10.07371319327652</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.62036673809275</v>
+        <v>13.90645623065607</v>
       </c>
       <c r="C3" t="n">
-        <v>21.71625921793945</v>
+        <v>18.47649179392497</v>
       </c>
       <c r="D3" t="n">
-        <v>68.25110039923827</v>
+        <v>54.69807334211104</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.48410909584747</v>
+        <v>39.3219407981975</v>
       </c>
       <c r="C4" t="n">
-        <v>73.43669177306991</v>
+        <v>91.30449999036186</v>
       </c>
       <c r="D4" t="n">
-        <v>140.275057225897</v>
+        <v>126.810387462152</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.88031856220246</v>
+        <v>62.88094045700822</v>
       </c>
       <c r="C5" t="n">
-        <v>190.5326857016997</v>
+        <v>234.5640702371692</v>
       </c>
       <c r="D5" t="n">
-        <v>133.6158625479909</v>
+        <v>122.8902688790945</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.56237117474674</v>
+        <v>56.35231822376692</v>
       </c>
       <c r="C6" t="n">
-        <v>306.3956045137956</v>
+        <v>343.5478828856076</v>
       </c>
       <c r="D6" t="n">
-        <v>76.43789450495242</v>
+        <v>67.90454345963914</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.54677671800324</v>
+        <v>19.52303484665207</v>
       </c>
       <c r="C7" t="n">
-        <v>308.6555877289717</v>
+        <v>326.8012305465655</v>
       </c>
       <c r="D7" t="n">
-        <v>42.81892612072463</v>
+        <v>40.24380189248525</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>199.3585975628785</v>
+        <v>211.0413952434156</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -3369,10 +3369,10 @@
         <v>1.774999849278233</v>
       </c>
       <c r="C9" t="n">
-        <v>69.55780659359074</v>
+        <v>70.77811898996953</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.31775176547326</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
         <v>25.19655482949439</v>
@@ -3397,7 +3397,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.92336692580652</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>16.65044106402591</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>10.75504610002381</v>
+      </c>
+      <c r="D14" t="n">
         <v>11.06233313145306</v>
-      </c>
-      <c r="D14" t="n">
-        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>6.808420328951629</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.383102588834508</v>
+        <v>4.531747402803277</v>
       </c>
       <c r="C2" t="n">
-        <v>10.63723637551419</v>
+        <v>2.857867567062465</v>
       </c>
       <c r="D2" t="n">
-        <v>16.17920216598744</v>
+        <v>8.47346443535422</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>10.15127126191202</v>
+        <v>11.10847527355266</v>
       </c>
       <c r="C3" t="n">
-        <v>17.10695374650067</v>
+        <v>13.8819125380499</v>
       </c>
       <c r="D3" t="n">
-        <v>63.91668428498858</v>
+        <v>50.79562621772997</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.17932533917445</v>
+        <v>33.24688600431823</v>
       </c>
       <c r="C4" t="n">
-        <v>64.73251662721769</v>
+        <v>71.95621623506572</v>
       </c>
       <c r="D4" t="n">
-        <v>141.3598884390897</v>
+        <v>125.0236066404228</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>57.80039608753097</v>
+        <v>61.85010536754907</v>
       </c>
       <c r="C5" t="n">
-        <v>166.6762164885023</v>
+        <v>207.0260471330462</v>
       </c>
       <c r="D5" t="n">
-        <v>147.8512042595697</v>
+        <v>133.051357618049</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.9472983902695</v>
+        <v>65.61019907481435</v>
       </c>
       <c r="C6" t="n">
-        <v>306.1540945785509</v>
+        <v>355.7843862713399</v>
       </c>
       <c r="D6" t="n">
-        <v>93.26308666033425</v>
+        <v>83.68319256229388</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.9794497181356</v>
+        <v>34.61446055633404</v>
       </c>
       <c r="C7" t="n">
-        <v>366.326393119542</v>
+        <v>391.6584291322225</v>
       </c>
       <c r="D7" t="n">
-        <v>50.66407202536089</v>
+        <v>46.95110220789945</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.095892479846697</v>
+        <v>9.763480918734528</v>
       </c>
       <c r="C8" t="n">
-        <v>278.3843790162255</v>
+        <v>294.4065015495335</v>
       </c>
       <c r="D8" t="n">
-        <v>36.30012136452581</v>
+        <v>35.71598148049896</v>
       </c>
     </row>
     <row r="9">
@@ -3680,10 +3680,10 @@
         <v>2.551562283337459</v>
       </c>
       <c r="C9" t="n">
-        <v>133.3468636770272</v>
+        <v>134.4562385828261</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.7117670855789376</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>48.54251523648354</v>
+        <v>47.97310156802039</v>
       </c>
       <c r="D10" t="n">
-        <v>26.33538216642069</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>27.8983245115816</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>20.39482680802324</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,7 +3750,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
         <v>11.06233313145306</v>
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>27.69215749368978</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.934664872171968</v>
+        <v>9.464047868939252</v>
       </c>
       <c r="C2" t="n">
-        <v>5.253331965424683</v>
+        <v>7.001824626688252</v>
       </c>
       <c r="D2" t="n">
-        <v>5.785439221126453</v>
+        <v>8.175013133263189</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.447497026687298</v>
+        <v>3.311435006424491</v>
       </c>
       <c r="C2" t="n">
-        <v>6.126105674500097</v>
+        <v>1.668971097219577</v>
       </c>
       <c r="D2" t="n">
-        <v>12.03720860177014</v>
+        <v>6.303802008968769</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.8819125380499</v>
+        <v>15.34471661737765</v>
       </c>
       <c r="C3" t="n">
-        <v>26.69372007847078</v>
+        <v>15.47725255745097</v>
       </c>
       <c r="D3" t="n">
-        <v>69.54209863032281</v>
+        <v>54.82570054366313</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.6740283711236</v>
+        <v>46.69879304790803</v>
       </c>
       <c r="C4" t="n">
-        <v>93.86980674155878</v>
+        <v>106.6325268967673</v>
       </c>
       <c r="D4" t="n">
-        <v>144.6526702391335</v>
+        <v>127.0145909846353</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.95650966803944</v>
+        <v>37.52730599483434</v>
       </c>
       <c r="C5" t="n">
-        <v>255.3771215672016</v>
+        <v>305.4953418690013</v>
       </c>
       <c r="D5" t="n">
-        <v>134.3030859409637</v>
+        <v>121.2949288596934</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.84406634594078</v>
+        <v>21.49438423677967</v>
       </c>
       <c r="C6" t="n">
-        <v>298.2647700272235</v>
+        <v>320.725194004982</v>
       </c>
       <c r="D6" t="n">
-        <v>74.7070733023653</v>
+        <v>67.05925868628265</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.988660995905543</v>
+        <v>6.467753875577986</v>
       </c>
       <c r="C7" t="n">
-        <v>195.7693279561522</v>
+        <v>207.0280106284546</v>
       </c>
       <c r="D7" t="n">
-        <v>31.9794497181356</v>
+        <v>31.08115056874977</v>
       </c>
     </row>
     <row r="8">
@@ -4288,10 +4288,10 @@
         <v>1.752419652080557</v>
       </c>
       <c r="C8" t="n">
-        <v>98.21894907137214</v>
+        <v>99.05343461998193</v>
       </c>
       <c r="D8" t="n">
-        <v>24.45042657426681</v>
+        <v>24.03318379996192</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.4437499623195582</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>37.05312185368311</v>
+        <v>36.60937189136354</v>
       </c>
       <c r="D9" t="n">
-        <v>20.07968579496001</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.78007281871549</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D10" t="n">
-        <v>19.21771131063132</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.81497376771187</v>
+        <v>15.10418842983717</v>
       </c>
       <c r="D11" t="n">
-        <v>16.34806277111788</v>
+        <v>15.99267010218054</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.66887328622834</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
         <v>9.105709956889166</v>
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.369980015780806</v>
+        <v>8.411614329986671</v>
       </c>
       <c r="C2" t="n">
-        <v>7.543749359432491</v>
+        <v>9.191122007158638</v>
       </c>
       <c r="D2" t="n">
-        <v>13.08473340220149</v>
+        <v>11.35391219961436</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.60564052252905</v>
+        <v>20.08655802888974</v>
       </c>
       <c r="C3" t="n">
-        <v>13.44503480966007</v>
+        <v>17.64200624531518</v>
       </c>
       <c r="D3" t="n">
-        <v>8.22704576158827</v>
+        <v>10.004009106275</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4669,7 +4669,7 @@
         <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39908940936015</v>
+        <v>13.39777181620793</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14817396665018</v>
+        <v>70.14127597897094</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576363459924723</v>
+        <v>1.576208448965639</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.002986300841745</v>
+        <v>5.383904410089508</v>
       </c>
       <c r="C2" t="n">
-        <v>6.677847884286804</v>
+        <v>11.66610796956485</v>
       </c>
       <c r="D2" t="n">
-        <v>17.18647531054466</v>
+        <v>14.3266442480737</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.29272504678157</v>
+        <v>25.54507526450201</v>
       </c>
       <c r="C3" t="n">
-        <v>23.73865948868788</v>
+        <v>29.03027961457818</v>
       </c>
       <c r="D3" t="n">
-        <v>17.22967220953152</v>
+        <v>17.12167996206437</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>14.66436545833461</v>
+        <v>23.12604892123787</v>
       </c>
       <c r="C4" t="n">
-        <v>21.02020009562846</v>
+        <v>27.43984833369835</v>
       </c>
       <c r="D4" t="n">
-        <v>19.38657191576176</v>
+        <v>20.31825048709199</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.50317890838889</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4994,7 +4994,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
         <v>44.86390658867074</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44359355735585</v>
+        <v>15.43939256444211</v>
       </c>
       <c r="C21" t="n">
-        <v>86.15899563577476</v>
+        <v>86.13555851741391</v>
       </c>
       <c r="D21" t="n">
-        <v>3.25128285418018</v>
+        <v>3.250398434619393</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.843943172753763</v>
+        <v>5.752059799182062</v>
       </c>
       <c r="C2" t="n">
-        <v>7.33758234154066</v>
+        <v>9.04582334693011</v>
       </c>
       <c r="D2" t="n">
-        <v>25.1003435544782</v>
+        <v>15.8218460016416</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.61884521104076</v>
+        <v>21.64753687864217</v>
       </c>
       <c r="C3" t="n">
-        <v>25.09838005906971</v>
+        <v>38.76921684070655</v>
       </c>
       <c r="D3" t="n">
-        <v>26.97842691270235</v>
+        <v>24.6075062069463</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.51191682673587</v>
+        <v>38.16053326407352</v>
       </c>
       <c r="C4" t="n">
-        <v>43.62297749050277</v>
+        <v>53.34817024877168</v>
       </c>
       <c r="D4" t="n">
-        <v>23.67484588791183</v>
+        <v>24.33850733598268</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>13.05724446648258</v>
+        <v>19.315886081056</v>
       </c>
       <c r="C5" t="n">
-        <v>24.39643045053324</v>
+        <v>31.19503330244241</v>
       </c>
       <c r="D5" t="n">
-        <v>29.42788743479815</v>
+        <v>29.96784867213389</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,7 +5246,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
         <v>29.89421759431538</v>
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>46.2138096820101</v>
       </c>
     </row>
     <row r="13">
@@ -5294,7 +5294,7 @@
         <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>45.00822350119503</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>27.65583282863265</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="D14" t="n">
         <v>45.47848065152925</v>
@@ -5319,7 +5319,7 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73919856339994</v>
+        <v>16.72918034573128</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1091112367396</v>
+        <v>102.0480001089608</v>
       </c>
       <c r="D21" t="n">
-        <v>5.021759569019982</v>
+        <v>4.18229508643282</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.828636120113313</v>
+        <v>6.471680866394974</v>
       </c>
       <c r="C2" t="n">
-        <v>13.02288329683394</v>
+        <v>6.369579105153306</v>
       </c>
       <c r="D2" t="n">
-        <v>23.39210254908875</v>
+        <v>22.96798754085413</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.50947030524186</v>
+        <v>20.54307071136451</v>
       </c>
       <c r="C3" t="n">
-        <v>27.03733177495716</v>
+        <v>36.64864179953343</v>
       </c>
       <c r="D3" t="n">
-        <v>40.05039759474863</v>
+        <v>31.15576339427253</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.73637719810989</v>
+        <v>39.93455136564751</v>
       </c>
       <c r="C4" t="n">
-        <v>54.34366242087795</v>
+        <v>76.78052445373456</v>
       </c>
       <c r="D4" t="n">
-        <v>31.42181702212341</v>
+        <v>30.82196917482861</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>27.75891633757857</v>
+        <v>38.28816046562561</v>
       </c>
       <c r="C5" t="n">
-        <v>54.48699758569799</v>
+        <v>67.54424205218056</v>
       </c>
       <c r="D5" t="n">
-        <v>31.02322745419922</v>
+        <v>31.66136346195964</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.87423848286517</v>
+        <v>15.77864910265474</v>
       </c>
       <c r="C6" t="n">
-        <v>26.20382797405162</v>
+        <v>31.51704654943536</v>
       </c>
       <c r="D6" t="n">
-        <v>38.11831811279092</v>
+        <v>38.19882142453915</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.623671834103982</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.25974653546468</v>
+        <v>21.13997331554657</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.54355373745002</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.16874709860598</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>9.82238578098934</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>48.68486865359933</v>
       </c>
     </row>
     <row r="11">
@@ -5571,7 +5571,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>9.062513057902304</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
         <v>33.58460721457913</v>
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.28066633689012</v>
       </c>
       <c r="D12" t="n">
-        <v>46.86470840992573</v>
+        <v>47.08167465256428</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>45.78871292607123</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>30.42141611149592</v>
+        <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>29.02537087605695</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5658,7 +5658,7 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
         <v>37.30543101367455</v>
@@ -5700,7 +5700,7 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>39.67733346713483</v>
       </c>
       <c r="D20" t="n">
         <v>16.13993225781756</v>
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.0662896222764</v>
+        <v>18.04774321844937</v>
       </c>
       <c r="C21" t="n">
-        <v>117.861032297708</v>
+        <v>117.7400390917888</v>
       </c>
       <c r="D21" t="n">
-        <v>6.882396046581486</v>
+        <v>6.015914406149791</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.919938656608266</v>
+        <v>7.561420818108934</v>
       </c>
       <c r="C2" t="n">
-        <v>10.27791671575986</v>
+        <v>7.526077900756048</v>
       </c>
       <c r="D2" t="n">
-        <v>29.81567777797563</v>
+        <v>23.8378160068168</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.81733817374786</v>
+        <v>18.98700060013331</v>
       </c>
       <c r="C3" t="n">
-        <v>38.08690218625501</v>
+        <v>28.07307560293754</v>
       </c>
       <c r="D3" t="n">
-        <v>46.02433237509047</v>
+        <v>39.21100330761761</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.14706653365455</v>
+        <v>28.65230674844316</v>
       </c>
       <c r="C4" t="n">
-        <v>51.71454206890498</v>
+        <v>71.01177494358029</v>
       </c>
       <c r="D4" t="n">
-        <v>38.16053326407352</v>
+        <v>34.03817465394117</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23.75829444277282</v>
+        <v>30.16419821298325</v>
       </c>
       <c r="C5" t="n">
-        <v>58.38944471007906</v>
+        <v>78.6625348027757</v>
       </c>
       <c r="D5" t="n">
-        <v>28.2252464970958</v>
+        <v>28.47068342315751</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.44405306195583</v>
+        <v>18.11324514335366</v>
       </c>
       <c r="C6" t="n">
-        <v>39.08435785376978</v>
+        <v>47.57745724320893</v>
       </c>
       <c r="D6" t="n">
-        <v>30.63151012020474</v>
+        <v>30.83276839957533</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.689227946110266</v>
+        <v>6.767186925373263</v>
       </c>
       <c r="C7" t="n">
-        <v>18.98405535702057</v>
+        <v>21.25974653546468</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>18.69247628885927</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.25738212942868</v>
       </c>
       <c r="D11" t="n">
-        <v>34.47308888692249</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5913,10 +5913,10 @@
         <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>19.25207248027995</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D13" t="n">
-        <v>30.69925071179776</v>
+        <v>30.43908757017236</v>
       </c>
     </row>
     <row r="14">
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5969,7 +5969,7 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
         <v>23.61103228713579</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.060954987779513</v>
+        <v>7.049542046565777</v>
       </c>
       <c r="C21" t="n">
-        <v>66.19645301043293</v>
+        <v>66.08945668655416</v>
       </c>
       <c r="D21" t="n">
-        <v>5.295716240834635</v>
+        <v>4.405963779103611</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.498768891486385</v>
+        <v>5.679410469067798</v>
       </c>
       <c r="C2" t="n">
-        <v>5.819800390775092</v>
+        <v>11.53651727260427</v>
       </c>
       <c r="D2" t="n">
-        <v>28.09663754783946</v>
+        <v>27.36719900358409</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.28152491140736</v>
+        <v>23.48831382410494</v>
       </c>
       <c r="C3" t="n">
-        <v>39.42698780255191</v>
+        <v>28.9026524130261</v>
       </c>
       <c r="D3" t="n">
-        <v>59.94551482131024</v>
+        <v>49.75988238974958</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.81371428256714</v>
+        <v>34.07646281440679</v>
       </c>
       <c r="C4" t="n">
-        <v>79.2437294436898</v>
+        <v>70.70546965985528</v>
       </c>
       <c r="D4" t="n">
-        <v>53.05462768520188</v>
+        <v>46.68603032775282</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.3668391506856</v>
+        <v>37.67456815047135</v>
       </c>
       <c r="C5" t="n">
-        <v>81.2150788338174</v>
+        <v>109.6121311791564</v>
       </c>
       <c r="D5" t="n">
-        <v>36.44738352016284</v>
+        <v>34.41025703385071</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.0704902127233</v>
+        <v>31.23528495831652</v>
       </c>
       <c r="C6" t="n">
-        <v>70.68190771495337</v>
+        <v>93.10208003683779</v>
       </c>
       <c r="D6" t="n">
-        <v>33.16736444027425</v>
+        <v>33.40887437551896</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.67788894201581</v>
+        <v>15.09142570968197</v>
       </c>
       <c r="C7" t="n">
-        <v>40.66300816219864</v>
+        <v>48.86747372658923</v>
       </c>
       <c r="D7" t="n">
-        <v>32.81786225756237</v>
+        <v>33.29695513723482</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.841398840268521</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="C8" t="n">
-        <v>22.86490403190821</v>
+        <v>24.53387512912779</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>31.71045084717197</v>
       </c>
     </row>
     <row r="9">
@@ -6168,7 +6168,7 @@
         <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.51874800293658</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
         <v>31.39530983410874</v>
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>32.97886888105885</v>
+        <v>33.1958351236974</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>30.95941385342317</v>
       </c>
     </row>
     <row r="14">
@@ -6235,10 +6235,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.66637001147211</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6280,7 +6280,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.282433087407705</v>
+        <v>7.267397444831624</v>
       </c>
       <c r="C21" t="n">
-        <v>75.55524328185496</v>
+        <v>75.3992484901281</v>
       </c>
       <c r="D21" t="n">
-        <v>6.372128951481742</v>
+        <v>5.450548083623718</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.809982913732624</v>
+        <v>5.413356841216912</v>
       </c>
       <c r="C2" t="n">
-        <v>4.044800541496859</v>
+        <v>7.51331518060084</v>
       </c>
       <c r="D2" t="n">
-        <v>23.65913792464388</v>
+        <v>27.79229575952295</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.15389770985527</v>
+        <v>21.30883392067702</v>
       </c>
       <c r="C3" t="n">
-        <v>29.39843500367074</v>
+        <v>38.23416434189203</v>
       </c>
       <c r="D3" t="n">
-        <v>68.51126354086367</v>
+        <v>59.48900213883547</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.3827680981318</v>
+        <v>40.64926369433918</v>
       </c>
       <c r="C4" t="n">
-        <v>89.78573629189205</v>
+        <v>70.98624950326987</v>
       </c>
       <c r="D4" t="n">
-        <v>71.17769030559801</v>
+        <v>59.89544568839366</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.60722846950583</v>
+        <v>44.8167826988669</v>
       </c>
       <c r="C5" t="n">
-        <v>118.4724042099839</v>
+        <v>121.4912784005428</v>
       </c>
       <c r="D5" t="n">
-        <v>46.92754026299754</v>
+        <v>43.44233591292137</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.29441080474959</v>
+        <v>42.10323204432872</v>
       </c>
       <c r="C6" t="n">
-        <v>102.8429807583746</v>
+        <v>136.9763849396278</v>
       </c>
       <c r="D6" t="n">
-        <v>37.55479493055324</v>
+        <v>36.58875518957439</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.66088043587412</v>
+        <v>26.52976821186155</v>
       </c>
       <c r="C7" t="n">
-        <v>74.13962312931062</v>
+        <v>94.50107051538947</v>
       </c>
       <c r="D7" t="n">
-        <v>35.39298648580176</v>
+        <v>35.81219275551515</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>11.59934912567606</v>
       </c>
       <c r="C8" t="n">
-        <v>39.47116644924301</v>
+        <v>45.56291095409447</v>
       </c>
       <c r="D8" t="n">
-        <v>33.88011327355743</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>26.84687272033327</v>
+        <v>27.73437264497238</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -6490,10 +6490,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>27.18950266911542</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
         <v>34.02246669067321</v>
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6524,7 +6524,7 @@
         <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>34.06370009425158</v>
+        <v>34.28066633689012</v>
       </c>
     </row>
     <row r="13">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
         <v>31.73990327829938</v>
@@ -6549,10 +6549,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.81737923147687</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.11412908006666</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6577,10 +6577,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>17.3592629064921</v>
+        <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6591,10 +6591,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>19.50241814486288</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.489875612021785</v>
+        <v>7.47024327852457</v>
       </c>
       <c r="C21" t="n">
-        <v>85.1973350867478</v>
+        <v>84.04023688340141</v>
       </c>
       <c r="D21" t="n">
-        <v>7.489875612021785</v>
+        <v>6.536462868708998</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_48_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_48_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497619613818</v>
+        <v>10.84497612262656</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907146775273</v>
+        <v>37.78907121160317</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.319509972236719</v>
+        <v>6.877142668248906</v>
       </c>
       <c r="C2" t="n">
-        <v>5.322054304721958</v>
+        <v>6.230170931150259</v>
       </c>
       <c r="D2" t="n">
-        <v>26.31476546463151</v>
+        <v>18.59430151843459</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.69385894719102</v>
+        <v>17.7598159698248</v>
       </c>
       <c r="C3" t="n">
-        <v>33.241977265797</v>
+        <v>27.40548716404971</v>
       </c>
       <c r="D3" t="n">
-        <v>66.83738370512286</v>
+        <v>52.27806525114266</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.85346721682252</v>
+        <v>39.9217886454923</v>
       </c>
       <c r="C4" t="n">
-        <v>83.00873188947631</v>
+        <v>44.08243541609028</v>
       </c>
       <c r="D4" t="n">
-        <v>74.44494666533139</v>
+        <v>71.73924999242718</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.40078371417351</v>
+        <v>48.00746273766904</v>
       </c>
       <c r="C5" t="n">
-        <v>126.3018421513522</v>
+        <v>85.75566196595889</v>
       </c>
       <c r="D5" t="n">
-        <v>53.4070751110265</v>
+        <v>61.80101798233672</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>51.15985461600555</v>
+        <v>42.18373535607696</v>
       </c>
       <c r="C6" t="n">
-        <v>163.5022261606723</v>
+        <v>106.9889013134089</v>
       </c>
       <c r="D6" t="n">
-        <v>41.74096714146165</v>
+        <v>45.76613272887356</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.32743037379547</v>
+        <v>28.38625312059227</v>
       </c>
       <c r="C7" t="n">
-        <v>145.8238952503</v>
+        <v>93.54288475604459</v>
       </c>
       <c r="D7" t="n">
-        <v>37.96811071404115</v>
+        <v>39.28561613314036</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.69385894719101</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="C8" t="n">
-        <v>83.86579763528377</v>
+        <v>64.42228435267569</v>
       </c>
       <c r="D8" t="n">
-        <v>35.9663271450819</v>
+        <v>36.71736413883071</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.764061755811273</v>
+        <v>7.321874378272709</v>
       </c>
       <c r="C9" t="n">
-        <v>42.15624642035802</v>
+        <v>39.160934174701</v>
       </c>
       <c r="D9" t="n">
-        <v>33.50312215512664</v>
+        <v>34.05780960802609</v>
       </c>
     </row>
     <row r="10">
@@ -895,10 +895,10 @@
         <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>30.46363126277853</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>30.03068052520567</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>28.42257778564941</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="D13" t="n">
-        <v>32.5203927031756</v>
+        <v>32.780555844801</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.66110142005238</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.72870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -979,10 +979,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>19.42584182393164</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>17.9443845382232</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1024,7 +1024,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.657164701394977</v>
+        <v>7.715853904659236</v>
       </c>
       <c r="C21" t="n">
-        <v>92.8431220044141</v>
+        <v>96.44817380824045</v>
       </c>
       <c r="D21" t="n">
-        <v>7.657164701394977</v>
+        <v>8.680335642741641</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.152032025438014</v>
+        <v>6.888923640699868</v>
       </c>
       <c r="C2" t="n">
-        <v>15.6667298643706</v>
+        <v>5.378013923864026</v>
       </c>
       <c r="D2" t="n">
-        <v>24.05870924027233</v>
+        <v>19.54561504384975</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.17491532227195</v>
+        <v>20.72469403665017</v>
       </c>
       <c r="C3" t="n">
-        <v>26.81152980298039</v>
+        <v>25.58434517267188</v>
       </c>
       <c r="D3" t="n">
-        <v>70.73492209098269</v>
+        <v>54.54099370943155</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.0283982346277</v>
+        <v>36.64176956560371</v>
       </c>
       <c r="C4" t="n">
-        <v>82.8555792476138</v>
+        <v>56.29635860462485</v>
       </c>
       <c r="D4" t="n">
-        <v>86.722683454642</v>
+        <v>80.64762866076273</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.93507544946203</v>
+        <v>53.62796834448203</v>
       </c>
       <c r="C5" t="n">
-        <v>137.1746979758856</v>
+        <v>83.47309855358506</v>
       </c>
       <c r="D5" t="n">
-        <v>65.55620295108078</v>
+        <v>71.74121348783568</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>59.61270234957058</v>
+        <v>53.5749539684527</v>
       </c>
       <c r="C6" t="n">
-        <v>180.8104381865436</v>
+        <v>120.6744643106095</v>
       </c>
       <c r="D6" t="n">
-        <v>47.37619896383834</v>
+        <v>54.17872880656449</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>48.32849423695774</v>
+        <v>38.86640986342697</v>
       </c>
       <c r="C7" t="n">
-        <v>185.3490578232766</v>
+        <v>124.3246022749991</v>
       </c>
       <c r="D7" t="n">
-        <v>41.08221443191203</v>
+        <v>42.99858595060179</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>29.45733986592554</v>
+        <v>22.03041848329842</v>
       </c>
       <c r="C8" t="n">
-        <v>132.0990623449296</v>
+        <v>94.04652132832319</v>
       </c>
       <c r="D8" t="n">
-        <v>37.55184968744049</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.42343636016663</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>69.89061906533041</v>
+        <v>58.79687000734145</v>
       </c>
       <c r="D9" t="n">
-        <v>35.05624702324509</v>
+        <v>35.83280945730432</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.690610604442014</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>39.14718970684157</v>
+        <v>38.86248287260999</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1217,10 +1217,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
         <v>36.60544490054656</v>
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>24.89024954576939</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1276,7 +1276,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>18.88882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1335,7 +1335,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.827696917858287</v>
+        <v>7.906426781614777</v>
       </c>
       <c r="C21" t="n">
-        <v>100.7815978174254</v>
+        <v>105.7484582040976</v>
       </c>
       <c r="D21" t="n">
-        <v>8.806159032590573</v>
+        <v>9.88303347701847</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.200538573573606</v>
+        <v>9.165596566848221</v>
       </c>
       <c r="C2" t="n">
-        <v>15.32508166329271</v>
+        <v>8.098436812331938</v>
       </c>
       <c r="D2" t="n">
-        <v>19.46805697521425</v>
+        <v>24.95013615572844</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.29901644363455</v>
+        <v>21.61317570899353</v>
       </c>
       <c r="C3" t="n">
-        <v>41.61628518302229</v>
+        <v>23.09561474240621</v>
       </c>
       <c r="D3" t="n">
-        <v>72.15354752361934</v>
+        <v>56.48976290236146</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.70107533848601</v>
+        <v>37.39477005476101</v>
       </c>
       <c r="C4" t="n">
-        <v>74.90440459091889</v>
+        <v>59.29559784109885</v>
       </c>
       <c r="D4" t="n">
-        <v>98.06874167262238</v>
+        <v>86.81202249572846</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>56.47503668679778</v>
+        <v>54.11884219660543</v>
       </c>
       <c r="C5" t="n">
-        <v>141.9361743414826</v>
+        <v>92.89787651435444</v>
       </c>
       <c r="D5" t="n">
-        <v>76.52723354603889</v>
+        <v>82.34408869370124</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>66.25422556880025</v>
+        <v>62.55107322838128</v>
       </c>
       <c r="C6" t="n">
-        <v>196.6293389450724</v>
+        <v>125.3436563920073</v>
       </c>
       <c r="D6" t="n">
-        <v>54.82275530055039</v>
+        <v>62.06805335789186</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>57.01205268102077</v>
+        <v>49.82565948593412</v>
       </c>
       <c r="C7" t="n">
-        <v>215.4121360227224</v>
+        <v>148.039699818785</v>
       </c>
       <c r="D7" t="n">
-        <v>43.95677170994669</v>
+        <v>48.02906118716245</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>38.30288668118931</v>
+        <v>30.87596529856218</v>
       </c>
       <c r="C8" t="n">
-        <v>177.661973299024</v>
+        <v>125.6735236206342</v>
       </c>
       <c r="D8" t="n">
-        <v>39.63806355896497</v>
+        <v>41.14013754646259</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19.63593583264045</v>
+        <v>15.75312366234431</v>
       </c>
       <c r="C9" t="n">
-        <v>108.1640533153923</v>
+        <v>84.7562428030356</v>
       </c>
       <c r="D9" t="n">
-        <v>36.0546844384641</v>
+        <v>37.60780930658255</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>55.94489292650449</v>
+        <v>53.09782458418874</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>36.30012136452581</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>37.31623023842126</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>37.13853390395258</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>34.49763257952867</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>3.121957699504857</v>
       </c>
       <c r="C13" t="n">
-        <v>29.65859814529614</v>
+        <v>31.21957699504857</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>34.08137155292803</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>28.27040689149115</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.74204670015712</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>19.83326712119407</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>24.55547357862122</v>
       </c>
     </row>
     <row r="18">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -1646,7 +1646,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.98160507926269</v>
+        <v>8.082761989737156</v>
       </c>
       <c r="C21" t="n">
-        <v>107.7516685700463</v>
+        <v>114.1690131050373</v>
       </c>
       <c r="D21" t="n">
-        <v>9.977006349078362</v>
+        <v>11.11379773588859</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.585964510715104</v>
+        <v>8.189739348826892</v>
       </c>
       <c r="C2" t="n">
-        <v>10.7884255219682</v>
+        <v>5.312236827679491</v>
       </c>
       <c r="D2" t="n">
-        <v>16.2665777116654</v>
+        <v>20.19356852865264</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.41744806294992</v>
+        <v>26.42864819832414</v>
       </c>
       <c r="C3" t="n">
-        <v>59.74916528046088</v>
+        <v>36.75663404700058</v>
       </c>
       <c r="D3" t="n">
-        <v>77.39117152577607</v>
+        <v>62.99384144299659</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.13354304997335</v>
+        <v>25.99766095615978</v>
       </c>
       <c r="C4" t="n">
-        <v>110.3975293425538</v>
+        <v>80.52000145921066</v>
       </c>
       <c r="D4" t="n">
-        <v>91.5214662330004</v>
+        <v>86.68439529417637</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.3064127613788</v>
+        <v>35.22019888985433</v>
       </c>
       <c r="C5" t="n">
-        <v>117.490656505737</v>
+        <v>74.88280614142548</v>
       </c>
       <c r="D5" t="n">
-        <v>53.30890034060182</v>
+        <v>60.0093284220863</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.38120551335081</v>
+        <v>30.91327171132357</v>
       </c>
       <c r="C6" t="n">
-        <v>141.8870869562703</v>
+        <v>97.48951052711678</v>
       </c>
       <c r="D6" t="n">
-        <v>28.94094057349173</v>
+        <v>31.5975498611836</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.3919226226395</v>
+        <v>20.4213339960379</v>
       </c>
       <c r="C7" t="n">
-        <v>124.9234683745896</v>
+        <v>88.33274968960676</v>
       </c>
       <c r="D7" t="n">
-        <v>27.84727363096077</v>
+        <v>28.92523261022377</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.60211444233956</v>
+        <v>10.93176068678823</v>
       </c>
       <c r="C8" t="n">
-        <v>79.69336989223483</v>
+        <v>62.4195190360122</v>
       </c>
       <c r="D8" t="n">
-        <v>26.53664044579129</v>
+        <v>27.70492021384499</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>42.71093387325747</v>
+        <v>40.49218406165969</v>
       </c>
       <c r="D9" t="n">
-        <v>27.06874770149305</v>
+        <v>27.62343515439249</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>29.18245050873644</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>29.04009709162065</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>3.198534020436107</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>27.54293184264426</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>2.386628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>24.0832529328785</v>
+        <v>25.38505038870978</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.77167905773377</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>24.97566159603886</v>
+        <v>25.49598787928967</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>24.89024954576939</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>18.63357142660446</v>
       </c>
       <c r="D15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.93362637120549</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>0.4133157834879072</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>16.94594712300419</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>20.66578917439536</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>18.41660518396592</v>
       </c>
     </row>
     <row r="18">
@@ -1943,7 +1943,7 @@
         <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
     </row>
     <row r="19">
@@ -1968,10 +1968,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>75.31968386981528</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>7.397468951499714</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.710425484976196</v>
+        <v>4.895975801078843</v>
       </c>
       <c r="C2" t="n">
-        <v>5.324017800130453</v>
+        <v>2.709623663721197</v>
       </c>
       <c r="D2" t="n">
-        <v>11.56989669454866</v>
+        <v>14.39143959655399</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.34029090494192</v>
+        <v>28.16634163484099</v>
       </c>
       <c r="C3" t="n">
-        <v>51.97372346282614</v>
+        <v>28.76029899591031</v>
       </c>
       <c r="D3" t="n">
-        <v>74.21030896401639</v>
+        <v>65.33530971762524</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.14402347955058</v>
+        <v>37.24161741289851</v>
       </c>
       <c r="C4" t="n">
-        <v>132.6174251327719</v>
+        <v>89.30075292599412</v>
       </c>
       <c r="D4" t="n">
-        <v>106.2879334525767</v>
+        <v>96.71589333617028</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.98796665230434</v>
+        <v>39.14718970684157</v>
       </c>
       <c r="C5" t="n">
-        <v>157.987749305918</v>
+        <v>111.4529081246192</v>
       </c>
       <c r="D5" t="n">
-        <v>66.83247496660162</v>
+        <v>73.65562151111696</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.33845058272045</v>
+        <v>37.6755498981756</v>
       </c>
       <c r="C6" t="n">
-        <v>165.756318889623</v>
+        <v>111.6580933948068</v>
       </c>
       <c r="D6" t="n">
-        <v>34.49566908412018</v>
+        <v>39.48687441251096</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.77498415374501</v>
+        <v>19.46314823669301</v>
       </c>
       <c r="C7" t="n">
-        <v>157.8012172421111</v>
+        <v>112.7065999429423</v>
       </c>
       <c r="D7" t="n">
-        <v>30.12296480940488</v>
+        <v>31.38058361854505</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.01520924164921</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>104.8948334602505</v>
+        <v>82.78096642209104</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>28.95664853675967</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>46.59374604355361</v>
+        <v>47.25937098703294</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>28.95468504135117</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>29.89421759431538</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>28.78680618392497</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>21.91359050649305</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.63954402828795</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>26.27647730416588</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>15.36435157146258</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>15.70599977254047</v>
       </c>
     </row>
     <row r="17">
@@ -2240,7 +2240,7 @@
         <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>12.27773678931061</v>
       </c>
     </row>
     <row r="18">
@@ -2265,10 +2265,10 @@
         <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>65.59743635465912</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>6.018113427032947</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.671155576806324</v>
+        <v>5.996514977539517</v>
       </c>
       <c r="C2" t="n">
-        <v>7.024404823885929</v>
+        <v>6.530585728649783</v>
       </c>
       <c r="D2" t="n">
-        <v>10.19250466549039</v>
+        <v>17.31508425980099</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.18611545764617</v>
+        <v>22.25131171675396</v>
       </c>
       <c r="C3" t="n">
-        <v>36.09395434663399</v>
+        <v>18.55012287174348</v>
       </c>
       <c r="D3" t="n">
-        <v>66.99446333780234</v>
+        <v>61.79120050529424</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.72958707963818</v>
+        <v>46.16275880138927</v>
       </c>
       <c r="C4" t="n">
-        <v>131.034847833526</v>
+        <v>79.90739089176064</v>
       </c>
       <c r="D4" t="n">
-        <v>117.1872964651248</v>
+        <v>106.4155606541288</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.90299657039137</v>
+        <v>47.44295780772712</v>
       </c>
       <c r="C5" t="n">
-        <v>198.4848421060989</v>
+        <v>140.2917469368692</v>
       </c>
       <c r="D5" t="n">
-        <v>85.92746781420209</v>
+        <v>89.73174016815848</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.45670227558657</v>
+        <v>45.16235789076178</v>
       </c>
       <c r="C6" t="n">
-        <v>206.1287297313646</v>
+        <v>143.9399214058504</v>
       </c>
       <c r="D6" t="n">
-        <v>44.84034464376883</v>
+        <v>51.44161620712438</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.59638818703009</v>
+        <v>30.48228446915921</v>
       </c>
       <c r="C7" t="n">
-        <v>194.2721627071758</v>
+        <v>138.338069005418</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>35.03366682604743</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.02212253330794</v>
+        <v>14.01935721664445</v>
       </c>
       <c r="C8" t="n">
-        <v>150.8749871886498</v>
+        <v>115.5762484824558</v>
       </c>
       <c r="D8" t="n">
-        <v>29.12354564648163</v>
+        <v>30.62561963397925</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.767186925373262</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="C9" t="n">
-        <v>81.09530561389926</v>
+        <v>73.32968127330699</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>30.06405994715006</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.989421759431538</v>
       </c>
       <c r="C10" t="n">
-        <v>40.9977841293468</v>
+        <v>43.56014563743098</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>1.776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>34.47308888692249</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>30.56376952861169</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.07347651356504</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>26.79680358741669</v>
       </c>
     </row>
     <row r="14">
@@ -2506,10 +2506,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.97365704290136</v>
       </c>
     </row>
     <row r="15">
@@ -2523,7 +2523,7 @@
         <v>15.76686813020377</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2551,7 +2551,7 @@
         <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>36.10868056219768</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>4.212679398923063</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.855904071653971</v>
+        <v>3.464587648286994</v>
       </c>
       <c r="C2" t="n">
-        <v>3.423354244708628</v>
+        <v>2.911863690796039</v>
       </c>
       <c r="D2" t="n">
-        <v>7.132397071353077</v>
+        <v>11.96554101936013</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.92595231602077</v>
+        <v>23.35577788403162</v>
       </c>
       <c r="C3" t="n">
-        <v>34.7980473770282</v>
+        <v>22.97289627937536</v>
       </c>
       <c r="D3" t="n">
-        <v>63.82341825308514</v>
+        <v>63.08219873637881</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.99233561147783</v>
+        <v>51.31889774409352</v>
       </c>
       <c r="C4" t="n">
-        <v>129.4522705342802</v>
+        <v>74.66191290796993</v>
       </c>
       <c r="D4" t="n">
-        <v>124.6024368753009</v>
+        <v>113.4861076201143</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.30827844579606</v>
+        <v>49.67643383488862</v>
       </c>
       <c r="C5" t="n">
-        <v>239.9145952253143</v>
+        <v>163.3628179866693</v>
       </c>
       <c r="D5" t="n">
-        <v>91.35162388016572</v>
+        <v>97.07030425740341</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.24536447726626</v>
+        <v>38.11831811279092</v>
       </c>
       <c r="C6" t="n">
-        <v>243.8445312854143</v>
+        <v>181.8167295833966</v>
       </c>
       <c r="D6" t="n">
-        <v>44.03531152628644</v>
+        <v>50.87809302488671</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.59992996275281</v>
+        <v>9.282424543653592</v>
       </c>
       <c r="C7" t="n">
-        <v>200.97946302259</v>
+        <v>148.5187926984575</v>
       </c>
       <c r="D7" t="n">
-        <v>32.99752208743954</v>
+        <v>35.33309987584271</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.673119072214817</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>102.641722479004</v>
+        <v>92.54444734082557</v>
       </c>
       <c r="D8" t="n">
-        <v>30.87596529856218</v>
+        <v>32.3780392860598</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>31.28437234352885</v>
+        <v>33.17030968338697</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>1.281180754042088</v>
       </c>
       <c r="C10" t="n">
-        <v>25.48126166372597</v>
+        <v>27.04714925199963</v>
       </c>
       <c r="D10" t="n">
-        <v>23.06125357275758</v>
+        <v>23.91537407545231</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>21.50125647070939</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.69662426385451</v>
       </c>
     </row>
     <row r="13">
@@ -2803,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -2820,7 +2820,7 @@
         <v>13.21334235145782</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.90016483380309</v>
       </c>
     </row>
     <row r="16">
@@ -2848,7 +2848,7 @@
         <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>9.506263020221864</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>3.21031499288707</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.279037332184346</v>
+        <v>3.955461500410399</v>
       </c>
       <c r="C2" t="n">
-        <v>2.615375884113503</v>
+        <v>5.814891652253858</v>
       </c>
       <c r="D2" t="n">
-        <v>14.12145897788612</v>
+        <v>17.67538566725957</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.61960597456675</v>
+        <v>17.49965282819939</v>
       </c>
       <c r="C3" t="n">
-        <v>24.27371198750239</v>
+        <v>16.75843331149305</v>
       </c>
       <c r="D3" t="n">
-        <v>56.02834148136547</v>
+        <v>58.87540982368122</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>44.03138453546944</v>
+        <v>48.83016731382786</v>
       </c>
       <c r="C4" t="n">
-        <v>109.1723082076538</v>
+        <v>66.36614480708438</v>
       </c>
       <c r="D4" t="n">
-        <v>127.1549809063426</v>
+        <v>118.2721276783175</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.07037670619884</v>
+        <v>62.24280444924779</v>
       </c>
       <c r="C5" t="n">
-        <v>241.1172361630167</v>
+        <v>152.219981543468</v>
       </c>
       <c r="D5" t="n">
-        <v>109.9066554904305</v>
+        <v>112.72918014014</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>49.22777513404782</v>
+        <v>50.59633143376788</v>
       </c>
       <c r="C6" t="n">
-        <v>304.3830217200896</v>
+        <v>219.8545443844393</v>
       </c>
       <c r="D6" t="n">
-        <v>58.08313942635406</v>
+        <v>65.77120569831082</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.85861263505523</v>
+        <v>21.79872602509618</v>
       </c>
       <c r="C7" t="n">
-        <v>266.6750741476738</v>
+        <v>202.7760613213617</v>
       </c>
       <c r="D7" t="n">
-        <v>36.47094546506476</v>
+        <v>40.8426679920758</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.425538724295373</v>
+        <v>6.091744504851458</v>
       </c>
       <c r="C8" t="n">
-        <v>165.3950357344601</v>
+        <v>138.0239097400591</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.440624792757569</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>64.12186955517615</v>
+        <v>64.89843198923538</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>33.28124717396686</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>32.59893251951534</v>
       </c>
       <c r="D10" t="n">
-        <v>24.34243432679967</v>
+        <v>25.48126166372597</v>
       </c>
     </row>
     <row r="11">
@@ -3083,10 +3083,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>25.05518316008284</v>
       </c>
       <c r="D11" t="n">
         <v>23.98900515327081</v>
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>22.34752299177014</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>16.1301147807751</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>16.3902779224005</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>14.74977750860408</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>34.94432778496098</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>4.722206457427158</v>
       </c>
     </row>
     <row r="18">
@@ -3184,7 +3184,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
         <v>1.070104997629023</v>
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.351285751671111</v>
+        <v>2.999239236474005</v>
       </c>
       <c r="C2" t="n">
-        <v>2.090140862341459</v>
+        <v>3.855323234577225</v>
       </c>
       <c r="D2" t="n">
-        <v>10.07371319327652</v>
+        <v>12.26301057374691</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.90645623065607</v>
+        <v>15.99267010218054</v>
       </c>
       <c r="C3" t="n">
-        <v>18.47649179392497</v>
+        <v>20.01292695107123</v>
       </c>
       <c r="D3" t="n">
-        <v>54.69807334211104</v>
+        <v>59.35155746024092</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.3219407981975</v>
+        <v>43.59745205019236</v>
       </c>
       <c r="C4" t="n">
-        <v>91.30449999036186</v>
+        <v>57.04935909378215</v>
       </c>
       <c r="D4" t="n">
-        <v>126.810387462152</v>
+        <v>121.9477910830175</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.88094045700822</v>
+        <v>68.86960145291376</v>
       </c>
       <c r="C5" t="n">
-        <v>234.5640702371692</v>
+        <v>145.445922384165</v>
       </c>
       <c r="D5" t="n">
-        <v>122.8902688790945</v>
+        <v>123.5774922720673</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>56.35231822376692</v>
+        <v>60.29698049943061</v>
       </c>
       <c r="C6" t="n">
-        <v>343.5478828856076</v>
+        <v>238.7325709894012</v>
       </c>
       <c r="D6" t="n">
-        <v>67.90454345963914</v>
+        <v>78.32972233103602</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.52303484665207</v>
+        <v>21.97838585497334</v>
       </c>
       <c r="C7" t="n">
-        <v>326.8012305465655</v>
+        <v>249.4876170894249</v>
       </c>
       <c r="D7" t="n">
-        <v>40.24380189248525</v>
+        <v>45.45393695892307</v>
       </c>
     </row>
     <row r="8">
@@ -3355,10 +3355,10 @@
         <v>5.090361846519712</v>
       </c>
       <c r="C8" t="n">
-        <v>211.0413952434156</v>
+        <v>176.5771420858313</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>36.21667280966483</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>70.77811898996953</v>
+        <v>79.87499321752047</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.90832191507333</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>24.52209415667683</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>20.82875929330033</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>11.70734137314322</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.91060420565131</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.67690719431156</v>
       </c>
     </row>
     <row r="15">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -3481,7 +3481,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
         <v>0.4722206457427158</v>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.531747402803277</v>
+        <v>5.616578615996002</v>
       </c>
       <c r="C2" t="n">
-        <v>2.857867567062465</v>
+        <v>6.08487227092173</v>
       </c>
       <c r="D2" t="n">
-        <v>8.47346443535422</v>
+        <v>23.08088852684251</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.10847527355266</v>
+        <v>13.12596680577985</v>
       </c>
       <c r="C3" t="n">
-        <v>13.8819125380499</v>
+        <v>17.42602175038088</v>
       </c>
       <c r="D3" t="n">
-        <v>50.79562621772997</v>
+        <v>55.70927347748525</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.24688600431823</v>
+        <v>37.2288546927433</v>
       </c>
       <c r="C4" t="n">
-        <v>71.95621623506572</v>
+        <v>53.59066193172064</v>
       </c>
       <c r="D4" t="n">
-        <v>125.0236066404228</v>
+        <v>123.2113003783832</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>61.85010536754907</v>
+        <v>68.32964021557801</v>
       </c>
       <c r="C5" t="n">
-        <v>207.0260471330462</v>
+        <v>126.9645218517188</v>
       </c>
       <c r="D5" t="n">
-        <v>133.051357618049</v>
+        <v>135.7757074973339</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>65.61019907481435</v>
+        <v>73.41902031439348</v>
       </c>
       <c r="C6" t="n">
-        <v>355.7843862713399</v>
+        <v>236.4784782604505</v>
       </c>
       <c r="D6" t="n">
-        <v>83.68319256229388</v>
+        <v>93.98761646606842</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>34.61446055633404</v>
+        <v>39.64493579289469</v>
       </c>
       <c r="C7" t="n">
-        <v>391.6584291322225</v>
+        <v>294.2828013387984</v>
       </c>
       <c r="D7" t="n">
-        <v>46.95110220789945</v>
+        <v>54.017722183068</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.763480918734528</v>
+        <v>11.18210635137117</v>
       </c>
       <c r="C8" t="n">
-        <v>294.4065015495335</v>
+        <v>240.1649408898972</v>
       </c>
       <c r="D8" t="n">
-        <v>35.71598148049896</v>
+        <v>38.97047512007713</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.551562283337459</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>134.4562385828261</v>
+        <v>135.2328010168853</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C10" t="n">
-        <v>47.97310156802039</v>
+        <v>56.51430659496764</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>27.18950266911542</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>29.852984190737</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>25.05518316008284</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>21.26269177857742</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>17.17076734727672</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.98419422574081</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>11.98419422574081</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
         <v>6.450082416901544</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.464047868939252</v>
+        <v>4.068362486398782</v>
       </c>
       <c r="C2" t="n">
-        <v>7.001824626688252</v>
+        <v>5.775621744083985</v>
       </c>
       <c r="D2" t="n">
-        <v>8.175013133263189</v>
+        <v>5.396667130244716</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.311435006424491</v>
+        <v>3.927972564691488</v>
       </c>
       <c r="C2" t="n">
-        <v>1.668971097219577</v>
+        <v>3.358558896228339</v>
       </c>
       <c r="D2" t="n">
-        <v>6.303802008968769</v>
+        <v>16.98816227428681</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.34471661737765</v>
+        <v>18.49121800948867</v>
       </c>
       <c r="C3" t="n">
-        <v>15.47725255745097</v>
+        <v>22.0991408225957</v>
       </c>
       <c r="D3" t="n">
-        <v>54.82570054366313</v>
+        <v>63.59270754258714</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.69879304790803</v>
+        <v>51.48481310611123</v>
       </c>
       <c r="C4" t="n">
-        <v>106.6325268967673</v>
+        <v>76.10410028550849</v>
       </c>
       <c r="D4" t="n">
-        <v>127.0145909846353</v>
+        <v>127.4485234699124</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.52730599483434</v>
+        <v>44.49771469498668</v>
       </c>
       <c r="C5" t="n">
-        <v>305.4953418690013</v>
+        <v>195.5395989933585</v>
       </c>
       <c r="D5" t="n">
-        <v>121.2949288596934</v>
+        <v>126.57182277002</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>21.49438423677967</v>
+        <v>24.59376173908685</v>
       </c>
       <c r="C6" t="n">
-        <v>320.725194004982</v>
+        <v>244.8105710263932</v>
       </c>
       <c r="D6" t="n">
-        <v>67.05925868628265</v>
+        <v>77.56494086942776</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.467753875577986</v>
+        <v>7.366053024963818</v>
       </c>
       <c r="C7" t="n">
-        <v>207.0280106284546</v>
+        <v>168.8802400845363</v>
       </c>
       <c r="D7" t="n">
-        <v>31.08115056874977</v>
+        <v>34.7941203862112</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.752419652080557</v>
+        <v>2.002765316663493</v>
       </c>
       <c r="C8" t="n">
-        <v>99.05343461998193</v>
+        <v>99.63757450400877</v>
       </c>
       <c r="D8" t="n">
-        <v>24.03318379996192</v>
+        <v>25.11801501315464</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>36.60937189136354</v>
+        <v>43.15468383557703</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.74531073843935</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>23.34596040698915</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>19.64477156197868</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.10418842983717</v>
+        <v>17.41424077792992</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>17.05884810899257</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.886199381765381</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>16.59349969717959</v>
       </c>
       <c r="D14" t="n">
         <v>5.223879534297279</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>25.083653843506</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>2.5083653843506</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.411614329986671</v>
+        <v>6.525676990128549</v>
       </c>
       <c r="C2" t="n">
-        <v>9.191122007158638</v>
+        <v>4.58279828342411</v>
       </c>
       <c r="D2" t="n">
-        <v>11.35391219961436</v>
+        <v>20.59510333968959</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.08655802888974</v>
+        <v>8.6491972744144</v>
       </c>
       <c r="C3" t="n">
-        <v>17.64200624531518</v>
+        <v>14.78512042595696</v>
       </c>
       <c r="D3" t="n">
-        <v>10.004009106275</v>
+        <v>7.883434065101888</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>25.60201663134832</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>24.19517217116264</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39777181620793</v>
+        <v>13.39938777827796</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14127597897094</v>
+        <v>70.14973601569048</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576208448965639</v>
+        <v>1.576398562150348</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.383904410089508</v>
+        <v>5.187554869240146</v>
       </c>
       <c r="C2" t="n">
-        <v>11.66610796956485</v>
+        <v>4.883213080923635</v>
       </c>
       <c r="D2" t="n">
-        <v>14.3266442480737</v>
+        <v>18.02783309308418</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.54507526450201</v>
+        <v>16.92042168269378</v>
       </c>
       <c r="C3" t="n">
-        <v>29.03027961457818</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D3" t="n">
-        <v>17.12167996206437</v>
+        <v>23.27723806769188</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.12604892123787</v>
+        <v>10.19741340401162</v>
       </c>
       <c r="C4" t="n">
-        <v>27.43984833369835</v>
+        <v>23.06223532046182</v>
       </c>
       <c r="D4" t="n">
-        <v>20.31825048709199</v>
+        <v>19.19513111343364</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.399612373357458</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>29.10881943091793</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.50317890838889</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.77743067523902</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4913,7 +4913,7 @@
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4921,10 +4921,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>9.318749208710722</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D9" t="n">
         <v>40.27030908049991</v>
@@ -4935,7 +4935,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>8.968265278294615</v>
       </c>
       <c r="C10" t="n">
         <v>27.3318560862312</v>
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>29.49759152179966</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,7 +4977,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
@@ -4991,10 +4991,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>25.81211064005714</v>
       </c>
       <c r="D14" t="n">
         <v>44.86390658867074</v>
@@ -5022,7 +5022,7 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
         <v>40.5049467818149</v>
@@ -5036,7 +5036,7 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
         <v>36.83321036793183</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43939256444211</v>
+        <v>15.44384257819353</v>
       </c>
       <c r="C21" t="n">
-        <v>86.13555851741391</v>
+        <v>86.16038490992183</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250398434619393</v>
+        <v>3.251335279619691</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.752059799182062</v>
+        <v>5.800165436690155</v>
       </c>
       <c r="C2" t="n">
-        <v>9.04582334693011</v>
+        <v>6.006332454581986</v>
       </c>
       <c r="D2" t="n">
-        <v>15.8218460016416</v>
+        <v>18.56877607812417</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.64753687864217</v>
+        <v>17.51928778228433</v>
       </c>
       <c r="C3" t="n">
-        <v>38.76921684070655</v>
+        <v>18.17215000560846</v>
       </c>
       <c r="D3" t="n">
-        <v>24.6075062069463</v>
+        <v>32.29459073119883</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.16053326407352</v>
+        <v>22.8835572382889</v>
       </c>
       <c r="C4" t="n">
-        <v>53.34817024877168</v>
+        <v>34.40829353844221</v>
       </c>
       <c r="D4" t="n">
-        <v>24.33850733598268</v>
+        <v>26.53369520267854</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19.315886081056</v>
+        <v>9.547496423800233</v>
       </c>
       <c r="C5" t="n">
-        <v>31.19503330244241</v>
+        <v>26.53173170727006</v>
       </c>
       <c r="D5" t="n">
-        <v>29.96784867213389</v>
+        <v>29.35425635697964</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>12.19625172985813</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.6290068454485</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.42913122440964</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.55323234577224</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>29.39843500367073</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,10 +5277,10 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.11100391050467</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>45.77987719673301</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>45.52854978444583</v>
       </c>
     </row>
     <row r="14">
@@ -5302,7 +5302,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
         <v>27.9631198600619</v>
@@ -5319,7 +5319,7 @@
         <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
         <v>43.00054944601029</v>
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72918034573128</v>
+        <v>16.74107406778242</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0480001089608</v>
+        <v>102.1205518134727</v>
       </c>
       <c r="D21" t="n">
-        <v>4.18229508643282</v>
+        <v>5.022322220334726</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.471680866394974</v>
+        <v>5.367214699117312</v>
       </c>
       <c r="C2" t="n">
-        <v>6.369579105153306</v>
+        <v>6.363688618927824</v>
       </c>
       <c r="D2" t="n">
-        <v>22.96798754085413</v>
+        <v>17.16978559957247</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.54307071136451</v>
+        <v>18.81519475189012</v>
       </c>
       <c r="C3" t="n">
-        <v>36.64864179953343</v>
+        <v>21.1910241961674</v>
       </c>
       <c r="D3" t="n">
-        <v>31.15576339427253</v>
+        <v>39.22082078466008</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.93455136564751</v>
+        <v>28.76717122984004</v>
       </c>
       <c r="C4" t="n">
-        <v>76.78052445373456</v>
+        <v>40.71307729511523</v>
       </c>
       <c r="D4" t="n">
-        <v>30.82196917482861</v>
+        <v>35.93981995706723</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.28816046562561</v>
+        <v>22.16295442337175</v>
       </c>
       <c r="C5" t="n">
-        <v>67.54424205218056</v>
+        <v>46.90299657039137</v>
       </c>
       <c r="D5" t="n">
-        <v>31.66136346195964</v>
+        <v>32.39767424014475</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>15.77864910265474</v>
+        <v>9.45913913041802</v>
       </c>
       <c r="C6" t="n">
-        <v>31.51704654943536</v>
+        <v>27.85414586489051</v>
       </c>
       <c r="D6" t="n">
-        <v>38.19882142453915</v>
+        <v>38.07806645691679</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.13997331554657</v>
+        <v>21.19985992550562</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>39.46527596301753</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>31.87734795689393</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.9468721174462</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>41.93437143919824</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>49.25428232206248</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>50.46575898910303</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.71459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>47.29864089520282</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>46.30903920932205</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>4.302018440009523</v>
       </c>
       <c r="C14" t="n">
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>45.47848065152925</v>
       </c>
     </row>
     <row r="15">
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5647,7 +5647,7 @@
         <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>37.77765165941727</v>
       </c>
     </row>
     <row r="18">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04774321844937</v>
+        <v>18.07312835900488</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7400390917888</v>
+        <v>117.905646913508</v>
       </c>
       <c r="D21" t="n">
-        <v>6.015914406149791</v>
+        <v>6.885001279620905</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.561420818108934</v>
+        <v>7.323837873681205</v>
       </c>
       <c r="C2" t="n">
-        <v>7.526077900756048</v>
+        <v>4.543528375254239</v>
       </c>
       <c r="D2" t="n">
-        <v>23.8378160068168</v>
+        <v>14.69283614175776</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.98700060013331</v>
+        <v>16.6062624173348</v>
       </c>
       <c r="C3" t="n">
-        <v>28.07307560293754</v>
+        <v>21.87824758914017</v>
       </c>
       <c r="D3" t="n">
-        <v>39.21100330761761</v>
+        <v>40.9683316982194</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.65230674844316</v>
+        <v>24.26193101505142</v>
       </c>
       <c r="C4" t="n">
-        <v>71.01177494358029</v>
+        <v>39.99836496642355</v>
       </c>
       <c r="D4" t="n">
-        <v>34.03817465394117</v>
+        <v>40.61097553387356</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.16419821298325</v>
+        <v>20.0521968592411</v>
       </c>
       <c r="C5" t="n">
-        <v>78.6625348027757</v>
+        <v>46.06851102178158</v>
       </c>
       <c r="D5" t="n">
-        <v>28.47068342315751</v>
+        <v>30.90050899116836</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>18.11324514335366</v>
+        <v>10.86794708601219</v>
       </c>
       <c r="C6" t="n">
-        <v>47.57745724320893</v>
+        <v>35.74347041621788</v>
       </c>
       <c r="D6" t="n">
-        <v>30.83276839957533</v>
+        <v>30.63151012020474</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.767186925373263</v>
+        <v>5.090361846519712</v>
       </c>
       <c r="C7" t="n">
-        <v>21.25974653546468</v>
+        <v>20.00212772632452</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>31.14103717870882</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.69247628885927</v>
+        <v>18.52557917913731</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>22.18749811597791</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>29.95312245657017</v>
       </c>
     </row>
     <row r="10">
@@ -5874,7 +5874,7 @@
         <v>21.35301256736813</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>33.73775985644164</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.25738212942868</v>
+        <v>20.61277479836603</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>34.29539255245382</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>32.32797015314322</v>
       </c>
     </row>
     <row r="13">
@@ -5927,10 +5927,10 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>29.80684204863741</v>
       </c>
     </row>
     <row r="15">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.049542046565777</v>
+        <v>7.066861142933804</v>
       </c>
       <c r="C21" t="n">
-        <v>66.08945668655416</v>
+        <v>67.13518085787113</v>
       </c>
       <c r="D21" t="n">
-        <v>4.405963779103611</v>
+        <v>5.300145857200353</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.679410469067798</v>
+        <v>5.812928156845365</v>
       </c>
       <c r="C2" t="n">
-        <v>11.53651727260427</v>
+        <v>3.814089830998858</v>
       </c>
       <c r="D2" t="n">
-        <v>27.36719900358409</v>
+        <v>16.25872373003143</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.48831382410494</v>
+        <v>22.32494279457247</v>
       </c>
       <c r="C3" t="n">
-        <v>28.9026524130261</v>
+        <v>19.16371518689774</v>
       </c>
       <c r="D3" t="n">
-        <v>49.75988238974958</v>
+        <v>43.60432428412209</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.07646281440679</v>
+        <v>29.77542612210151</v>
       </c>
       <c r="C4" t="n">
-        <v>70.70546965985528</v>
+        <v>49.69803228438204</v>
       </c>
       <c r="D4" t="n">
-        <v>46.68603032775282</v>
+        <v>53.28435664799564</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>37.67456815047135</v>
+        <v>29.74695543867836</v>
       </c>
       <c r="C5" t="n">
-        <v>109.6121311791564</v>
+        <v>63.76451339083034</v>
       </c>
       <c r="D5" t="n">
-        <v>34.41025703385071</v>
+        <v>39.17173339944774</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.23528495831652</v>
+        <v>20.60884780754905</v>
       </c>
       <c r="C6" t="n">
-        <v>93.10208003683779</v>
+        <v>58.56615929684348</v>
       </c>
       <c r="D6" t="n">
-        <v>33.40887437551896</v>
+        <v>34.21390749300134</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>15.09142570968197</v>
+        <v>9.761517423326035</v>
       </c>
       <c r="C7" t="n">
-        <v>48.86747372658923</v>
+        <v>39.16584291322225</v>
       </c>
       <c r="D7" t="n">
-        <v>33.29695513723482</v>
+        <v>33.59638818703009</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.342090169434394</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>24.53387512912779</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>31.71045084717197</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>23.40781051235669</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.50624732468863</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>34.82848155585983</v>
       </c>
     </row>
     <row r="12">
@@ -6210,10 +6210,10 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>22.56448923440869</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>33.41280136633594</v>
       </c>
     </row>
     <row r="13">
@@ -6224,10 +6224,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>21.33337761328319</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>31.21957699504857</v>
       </c>
     </row>
     <row r="14">
@@ -6252,7 +6252,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.86552592671396</v>
       </c>
     </row>
     <row r="17">
@@ -6311,7 +6311,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6325,7 +6325,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.267397444831624</v>
+        <v>7.294713244712785</v>
       </c>
       <c r="C21" t="n">
-        <v>75.3992484901281</v>
+        <v>77.50632822507333</v>
       </c>
       <c r="D21" t="n">
-        <v>5.450548083623718</v>
+        <v>6.382874089123686</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.413356841216912</v>
+        <v>4.360923302264331</v>
       </c>
       <c r="C2" t="n">
-        <v>7.51331518060084</v>
+        <v>9.127308406382596</v>
       </c>
       <c r="D2" t="n">
-        <v>27.79229575952295</v>
+        <v>20.98289368286708</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.30883392067702</v>
+        <v>21.1762979806037</v>
       </c>
       <c r="C3" t="n">
-        <v>38.23416434189203</v>
+        <v>16.47863521578271</v>
       </c>
       <c r="D3" t="n">
-        <v>59.48900213883547</v>
+        <v>46.72628198362694</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>40.64926369433918</v>
+        <v>38.14777054391831</v>
       </c>
       <c r="C4" t="n">
-        <v>70.98624950326987</v>
+        <v>48.72806555258618</v>
       </c>
       <c r="D4" t="n">
-        <v>59.89544568839366</v>
+        <v>63.77531261557705</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.8167826988669</v>
+        <v>38.4599663138688</v>
       </c>
       <c r="C5" t="n">
-        <v>121.4912784005428</v>
+        <v>80.45422436302613</v>
       </c>
       <c r="D5" t="n">
-        <v>43.44233591292137</v>
+        <v>50.11822030179968</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.10323204432872</v>
+        <v>31.43654323768712</v>
       </c>
       <c r="C6" t="n">
-        <v>136.9763849396278</v>
+        <v>83.03916606830798</v>
       </c>
       <c r="D6" t="n">
-        <v>36.58875518957439</v>
+        <v>38.84284791852506</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.52976821186155</v>
+        <v>18.02586959767568</v>
       </c>
       <c r="C7" t="n">
-        <v>94.50107051538947</v>
+        <v>64.97697180557515</v>
       </c>
       <c r="D7" t="n">
-        <v>35.81219275551515</v>
+        <v>36.47094546506476</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.59934912567606</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>45.56291095409447</v>
+        <v>39.47116644924301</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.657812019574366</v>
       </c>
       <c r="C9" t="n">
-        <v>27.73437264497238</v>
+        <v>27.5124976638126</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>27.00984283923824</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.18387422479719</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>34.49763257952867</v>
       </c>
     </row>
     <row r="13">
@@ -6535,10 +6535,10 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.41468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>31.73990327829938</v>
+        <v>32.00006641992479</v>
       </c>
     </row>
     <row r="14">
@@ -6552,7 +6552,7 @@
         <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
         <v>28.66703296400686</v>
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -6605,10 +6605,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>21.40209995258047</v>
       </c>
     </row>
     <row r="19">
@@ -6622,7 +6622,7 @@
         <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.85071759569225</v>
       </c>
     </row>
     <row r="20">
@@ -6636,7 +6636,7 @@
         <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>10.08745766113597</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.47024327852457</v>
+        <v>7.511747602117198</v>
       </c>
       <c r="C21" t="n">
-        <v>84.04023688340141</v>
+        <v>87.32406587461242</v>
       </c>
       <c r="D21" t="n">
-        <v>6.536462868708998</v>
+        <v>7.511747602117198</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_48_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_48_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497612262656</v>
+        <v>10.84497643729387</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907121160317</v>
+        <v>37.78907230805421</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.877142668248906</v>
+        <v>1.685660808191773</v>
       </c>
       <c r="C2" t="n">
-        <v>6.230170931150259</v>
+        <v>2.749875319595316</v>
       </c>
       <c r="D2" t="n">
-        <v>18.59430151843459</v>
+        <v>12.17956201888593</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.7598159698248</v>
+        <v>13.87209506100743</v>
       </c>
       <c r="C3" t="n">
-        <v>27.40548716404971</v>
+        <v>26.01631416254048</v>
       </c>
       <c r="D3" t="n">
-        <v>52.27806525114266</v>
+        <v>62.72876956284995</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>39.9217886454923</v>
+        <v>23.49616780573891</v>
       </c>
       <c r="C4" t="n">
-        <v>44.08243541609028</v>
+        <v>78.3631017529804</v>
       </c>
       <c r="D4" t="n">
-        <v>71.73924999242718</v>
+        <v>73.92167513896783</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>48.00746273766904</v>
+        <v>25.0100227656875</v>
       </c>
       <c r="C5" t="n">
-        <v>85.75566196595889</v>
+        <v>88.52909923045614</v>
       </c>
       <c r="D5" t="n">
-        <v>61.80101798233672</v>
+        <v>47.1238898038469</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.18373535607696</v>
+        <v>16.46292725251477</v>
       </c>
       <c r="C6" t="n">
-        <v>106.9889013134089</v>
+        <v>53.97747052719389</v>
       </c>
       <c r="D6" t="n">
-        <v>45.76613272887356</v>
+        <v>30.30949687321178</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>28.38625312059227</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>93.54288475604459</v>
+        <v>30.42239785920016</v>
       </c>
       <c r="D7" t="n">
-        <v>39.28561613314036</v>
+        <v>29.76364514965055</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.10280577150543</v>
+        <v>6.175193059712437</v>
       </c>
       <c r="C8" t="n">
-        <v>64.42228435267569</v>
+        <v>27.62147165898401</v>
       </c>
       <c r="D8" t="n">
-        <v>36.71736413883071</v>
+        <v>30.87596529856218</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.321874378272709</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>39.160934174701</v>
+        <v>32.39374724932775</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>35.72187196672443</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>30.46363126277853</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>38.43542262126263</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>30.03068052520567</v>
+        <v>31.27455486648638</v>
       </c>
       <c r="D11" t="n">
-        <v>35.89465956267188</v>
+        <v>37.6716229073586</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>28.42257778564941</v>
+        <v>24.0832529328785</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>37.75212621910684</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.75615102091507</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.66110142005238</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.50027472300514</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.42584182393164</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>17.9443845382232</v>
+        <v>24.55547357862122</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>11.4344155113626</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>85.45721066386785</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.715853904659236</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>96.44817380824045</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.680335642741641</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.888923640699868</v>
+        <v>1.650317890838888</v>
       </c>
       <c r="C2" t="n">
-        <v>5.378013923864026</v>
+        <v>5.605779391249286</v>
       </c>
       <c r="D2" t="n">
-        <v>19.54561504384975</v>
+        <v>15.02957560431442</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.72469403665017</v>
+        <v>9.44932165337555</v>
       </c>
       <c r="C3" t="n">
-        <v>25.58434517267188</v>
+        <v>16.72898088036565</v>
       </c>
       <c r="D3" t="n">
-        <v>54.54099370943155</v>
+        <v>57.91820581204058</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.64176956560371</v>
+        <v>25.75516927321083</v>
       </c>
       <c r="C4" t="n">
-        <v>56.29635860462485</v>
+        <v>71.40741926839175</v>
       </c>
       <c r="D4" t="n">
-        <v>80.64762866076273</v>
+        <v>88.79024411978578</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>53.62796834448203</v>
+        <v>30.704159450319</v>
       </c>
       <c r="C5" t="n">
-        <v>83.47309855358506</v>
+        <v>120.9513171632071</v>
       </c>
       <c r="D5" t="n">
-        <v>71.74121348783568</v>
+        <v>63.00365892003907</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.5749539684527</v>
+        <v>25.318291544821</v>
       </c>
       <c r="C6" t="n">
-        <v>120.6744643106095</v>
+        <v>99.78385491194157</v>
       </c>
       <c r="D6" t="n">
-        <v>54.17872880656449</v>
+        <v>37.99756314516856</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>38.86640986342697</v>
+        <v>12.75584792127881</v>
       </c>
       <c r="C7" t="n">
-        <v>124.3246022749991</v>
+        <v>55.93409370175777</v>
       </c>
       <c r="D7" t="n">
-        <v>42.99858595060179</v>
+        <v>32.27888276793088</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>22.03041848329842</v>
+        <v>7.009678608322226</v>
       </c>
       <c r="C8" t="n">
-        <v>94.04652132832319</v>
+        <v>34.63115026730623</v>
       </c>
       <c r="D8" t="n">
-        <v>39.13737222979909</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>6.323436963053704</v>
       </c>
       <c r="C9" t="n">
-        <v>58.79687000734145</v>
+        <v>34.83437204208531</v>
       </c>
       <c r="D9" t="n">
-        <v>35.83280945730432</v>
+        <v>36.38749691020377</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.26355035309465</v>
+        <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
+        <v>35.3036474447153</v>
+      </c>
+      <c r="D10" t="n">
         <v>38.86248287260999</v>
-      </c>
-      <c r="D10" t="n">
-        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>38.73780091417063</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>38.61999118966103</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>28.35778243716912</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>36.68300296918207</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>21.81737923147687</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>23.29196428325557</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.66578917439536</v>
+        <v>25.62557857625024</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.88882582970863</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>16.52772260099505</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>9.095892479846698</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>50.2949348885641</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>47.54309607356029</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.906426781614777</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>105.7484582040976</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.88303347701847</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9.165596566848221</v>
+        <v>0.8541205026947251</v>
       </c>
       <c r="C2" t="n">
-        <v>8.098436812331938</v>
+        <v>2.219731559302038</v>
       </c>
       <c r="D2" t="n">
-        <v>24.95013615572844</v>
+        <v>10.13850854175681</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.61317570899353</v>
+        <v>8.732645829275379</v>
       </c>
       <c r="C3" t="n">
-        <v>23.09561474240621</v>
+        <v>20.58724935805562</v>
       </c>
       <c r="D3" t="n">
-        <v>56.48976290236146</v>
+        <v>58.54652434275854</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.39477005476101</v>
+        <v>28.39705234533899</v>
       </c>
       <c r="C4" t="n">
-        <v>59.29559784109885</v>
+        <v>65.9322123218073</v>
       </c>
       <c r="D4" t="n">
-        <v>86.81202249572846</v>
+        <v>97.46889382532758</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>54.11884219660543</v>
+        <v>31.51410130632262</v>
       </c>
       <c r="C5" t="n">
-        <v>92.89787651435444</v>
+        <v>140.5617275555371</v>
       </c>
       <c r="D5" t="n">
-        <v>82.34408869370124</v>
+        <v>72.1339125695344</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>62.55107322838128</v>
+        <v>19.52205309894783</v>
       </c>
       <c r="C6" t="n">
-        <v>125.3436563920073</v>
+        <v>131.7436696759922</v>
       </c>
       <c r="D6" t="n">
-        <v>62.06805335789186</v>
+        <v>38.9233512302733</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>49.82565948593412</v>
+        <v>4.73104218676538</v>
       </c>
       <c r="C7" t="n">
-        <v>148.039699818785</v>
+        <v>56.17364014159399</v>
       </c>
       <c r="D7" t="n">
-        <v>48.02906118716245</v>
+        <v>33.89582123682538</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30.87596529856218</v>
+        <v>4.339324852770902</v>
       </c>
       <c r="C8" t="n">
-        <v>125.6735236206342</v>
+        <v>38.55323234577224</v>
       </c>
       <c r="D8" t="n">
-        <v>41.14013754646259</v>
+        <v>36.71736413883071</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15.75312366234431</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>84.7562428030356</v>
+        <v>26.95781021091316</v>
       </c>
       <c r="D9" t="n">
-        <v>37.60780930658255</v>
+        <v>41.04687151455913</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.114144775599888</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>53.09782458418874</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>36.30012136452581</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>38.20471191076462</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="D11" t="n">
-        <v>37.13853390395258</v>
+        <v>30.91916219754903</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.339324852770901</v>
+        <v>1.301797455831271</v>
       </c>
       <c r="C12" t="n">
-        <v>34.49763257952867</v>
+        <v>18.65909686691488</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>29.94134148411922</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.121957699504857</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>31.21957699504857</v>
+        <v>17.95125677215293</v>
       </c>
       <c r="D13" t="n">
-        <v>34.08137155292803</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.151009220004762</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>28.27040689149115</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>31.03599017435442</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>21.50027472300514</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>18.27523351455437</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>22.31905230834699</v>
+        <v>22.7323680918349</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>14.05273663858884</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>7.083309686140737</v>
       </c>
       <c r="C17" t="n">
-        <v>19.83326712119407</v>
+        <v>43.44429940832985</v>
       </c>
       <c r="D17" t="n">
-        <v>24.55547357862122</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>41.1990424087174</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.082761989737156</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>114.1690131050373</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11.11379773588859</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.189739348826892</v>
+        <v>1.044579557318606</v>
       </c>
       <c r="C2" t="n">
-        <v>5.312236827679491</v>
+        <v>4.043818793792612</v>
       </c>
       <c r="D2" t="n">
-        <v>20.19356852865264</v>
+        <v>9.014407420394212</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>26.42864819832414</v>
+        <v>5.654866776461628</v>
       </c>
       <c r="C3" t="n">
-        <v>36.75663404700058</v>
+        <v>13.64629308903066</v>
       </c>
       <c r="D3" t="n">
-        <v>62.99384144299659</v>
+        <v>53.63287708300325</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.99766095615978</v>
+        <v>22.92184539875453</v>
       </c>
       <c r="C4" t="n">
-        <v>80.52000145921066</v>
+        <v>58.40220743023426</v>
       </c>
       <c r="D4" t="n">
-        <v>86.68439529417637</v>
+        <v>104.4883899106923</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.22019888985433</v>
+        <v>37.57639338004667</v>
       </c>
       <c r="C5" t="n">
-        <v>74.88280614142548</v>
+        <v>131.8487166803467</v>
       </c>
       <c r="D5" t="n">
-        <v>60.0093284220863</v>
+        <v>89.85445863118933</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>30.91327171132357</v>
+        <v>30.22899356146354</v>
       </c>
       <c r="C6" t="n">
-        <v>97.48951052711678</v>
+        <v>181.2532064011589</v>
       </c>
       <c r="D6" t="n">
-        <v>31.5975498611836</v>
+        <v>51.72337779824321</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.4213339960379</v>
+        <v>12.03720860177014</v>
       </c>
       <c r="C7" t="n">
-        <v>88.33274968960676</v>
+        <v>121.6297048268416</v>
       </c>
       <c r="D7" t="n">
-        <v>28.92523261022377</v>
+        <v>37.36924461445059</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.93176068678823</v>
+        <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>62.4195190360122</v>
+        <v>55.99398031171682</v>
       </c>
       <c r="D8" t="n">
-        <v>27.70492021384499</v>
+        <v>37.96909246174539</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.768749510154256</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>40.49218406165969</v>
+        <v>36.94218436310322</v>
       </c>
       <c r="D9" t="n">
-        <v>27.62343515439249</v>
+        <v>41.82343394861835</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>2.2776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>29.04009709162065</v>
+        <v>32.45657910239955</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.198534020436107</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>27.54293184264426</v>
+        <v>27.18753917370691</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.386628669023996</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>25.38505038870978</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>27.77167905773377</v>
+        <v>31.02617269731195</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.560978849752429</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>20.89551813718911</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>21.51009220004762</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>18.63357142660446</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>22.93362637120549</v>
+        <v>17.5585576904542</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>16.94594712300419</v>
+        <v>36.78510473042374</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>12.39947350463721</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>48.16650586575701</v>
       </c>
       <c r="D17" t="n">
-        <v>18.41660518396592</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>75.31968386981528</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.895975801078843</v>
+        <v>0.5713771638716436</v>
       </c>
       <c r="C2" t="n">
-        <v>2.709623663721197</v>
+        <v>2.18831563276614</v>
       </c>
       <c r="D2" t="n">
-        <v>14.39143959655399</v>
+        <v>6.918376071827272</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>28.16634163484099</v>
+        <v>4.786020058203201</v>
       </c>
       <c r="C3" t="n">
-        <v>28.76029899591031</v>
+        <v>14.99128744384879</v>
       </c>
       <c r="D3" t="n">
-        <v>65.33530971762524</v>
+        <v>49.22482989093507</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.24161741289851</v>
+        <v>18.49318150489717</v>
       </c>
       <c r="C4" t="n">
-        <v>89.30075292599412</v>
+        <v>47.64323433939346</v>
       </c>
       <c r="D4" t="n">
-        <v>96.71589333617028</v>
+        <v>109.0191555657913</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.14718970684157</v>
+        <v>38.99992755120455</v>
       </c>
       <c r="C5" t="n">
-        <v>111.4529081246192</v>
+        <v>125.5409876805609</v>
       </c>
       <c r="D5" t="n">
-        <v>73.65562151111696</v>
+        <v>103.7707323388879</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.6755498981756</v>
+        <v>36.91076843656734</v>
       </c>
       <c r="C6" t="n">
-        <v>111.6580933948068</v>
+        <v>203.7941336906657</v>
       </c>
       <c r="D6" t="n">
-        <v>39.48687441251096</v>
+        <v>62.18880832551422</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.46314823669301</v>
+        <v>14.43267300013236</v>
       </c>
       <c r="C7" t="n">
-        <v>112.7065999429423</v>
+        <v>176.3061797194592</v>
       </c>
       <c r="D7" t="n">
-        <v>31.38058361854505</v>
+        <v>41.14210104187108</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>82.78096642209104</v>
+        <v>87.03684272000096</v>
       </c>
       <c r="D8" t="n">
-        <v>28.95664853675967</v>
+        <v>41.39048321104552</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.77031209493525</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>47.25937098703294</v>
+        <v>47.92499593051228</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>42.04530892977813</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>1.565887588273662</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>33.45305302221006</v>
       </c>
       <c r="D10" t="n">
-        <v>29.89421759431538</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.7107853378746906</v>
       </c>
       <c r="C11" t="n">
-        <v>30.56376952861169</v>
+        <v>28.07602084605028</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>21.91359050649305</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="D12" t="n">
-        <v>28.63954402828795</v>
+        <v>29.72437524148068</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>17.17076734727672</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>24.71549845441346</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.36435157146258</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>14.33351648200343</v>
+        <v>31.17539834835746</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>40.91826256530281</v>
       </c>
       <c r="D16" t="n">
-        <v>15.70599977254047</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>12.27773678931061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>65.59743635465912</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.996514977539517</v>
+        <v>0.7264933011426397</v>
       </c>
       <c r="C2" t="n">
-        <v>6.530585728649783</v>
+        <v>11.17621586514569</v>
       </c>
       <c r="D2" t="n">
-        <v>17.31508425980099</v>
+        <v>6.908558594784804</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.25131171675396</v>
+        <v>3.328124717396687</v>
       </c>
       <c r="C3" t="n">
-        <v>18.55012287174348</v>
+        <v>11.48644813968768</v>
       </c>
       <c r="D3" t="n">
-        <v>61.79120050529424</v>
+        <v>43.72704274715294</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>46.16275880138927</v>
+        <v>13.84755136840126</v>
       </c>
       <c r="C4" t="n">
-        <v>79.90739089176064</v>
+        <v>42.23184099358505</v>
       </c>
       <c r="D4" t="n">
-        <v>106.4155606541288</v>
+        <v>108.9808674053257</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.44295780772712</v>
+        <v>34.7538687303371</v>
       </c>
       <c r="C5" t="n">
-        <v>140.2917469368692</v>
+        <v>107.5259173076319</v>
       </c>
       <c r="D5" t="n">
-        <v>89.73174016815848</v>
+        <v>117.8833555874358</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.16235789076178</v>
+        <v>44.59883470852411</v>
       </c>
       <c r="C6" t="n">
-        <v>143.9399214058504</v>
+        <v>202.7073389820644</v>
       </c>
       <c r="D6" t="n">
-        <v>51.44161620712438</v>
+        <v>77.92720577229484</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.48228446915921</v>
+        <v>26.94897448157494</v>
       </c>
       <c r="C7" t="n">
-        <v>138.338069005418</v>
+        <v>235.1148306992516</v>
       </c>
       <c r="D7" t="n">
-        <v>35.03366682604743</v>
+        <v>48.26860762699867</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.01935721664445</v>
+        <v>8.845546815263761</v>
       </c>
       <c r="C8" t="n">
-        <v>115.5762484824558</v>
+        <v>154.6301721573939</v>
       </c>
       <c r="D8" t="n">
-        <v>30.62561963397925</v>
+        <v>43.14290286312608</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.434374453633594</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="C9" t="n">
-        <v>73.32968127330699</v>
+        <v>74.88280614142545</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>43.59843379789659</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.989421759431538</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>43.56014563743098</v>
+        <v>44.12955930589413</v>
       </c>
       <c r="D10" t="n">
-        <v>30.32127784566274</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.776963344686726</v>
+        <v>0.8884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>34.47308888692249</v>
+        <v>32.69612554223576</v>
       </c>
       <c r="D11" t="n">
-        <v>30.56376952861169</v>
+        <v>33.7623035490478</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>1.084831213192725</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>26.90381408717959</v>
+        <v>27.55471281509523</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>19.77239876353076</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>26.79680358741669</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>16.90078672860884</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>19.97365704290136</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>31.17539834835746</v>
       </c>
       <c r="D15" t="n">
-        <v>17.5585576904542</v>
+        <v>10.0334615374024</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.87936820556466</v>
+        <v>42.98484148274235</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0.9444412914854317</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.464587648286994</v>
+        <v>0.476147636559703</v>
       </c>
       <c r="C2" t="n">
-        <v>2.911863690796039</v>
+        <v>5.542947538177491</v>
       </c>
       <c r="D2" t="n">
-        <v>11.96554101936013</v>
+        <v>4.91855599827652</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>23.35577788403162</v>
+        <v>4.717297718905924</v>
       </c>
       <c r="C3" t="n">
-        <v>22.97289627937536</v>
+        <v>25.80523840612741</v>
       </c>
       <c r="D3" t="n">
-        <v>63.08219873637881</v>
+        <v>46.20595570037614</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.31889774409352</v>
+        <v>23.27920156310037</v>
       </c>
       <c r="C4" t="n">
-        <v>74.66191290796993</v>
+        <v>59.15520791939156</v>
       </c>
       <c r="D4" t="n">
-        <v>113.4861076201143</v>
+        <v>114.4688370720654</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.67643383488862</v>
+        <v>28.32342126752049</v>
       </c>
       <c r="C5" t="n">
-        <v>163.3628179866693</v>
+        <v>165.6453813990431</v>
       </c>
       <c r="D5" t="n">
-        <v>97.07030425740341</v>
+        <v>110.6184225760094</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.11831811279092</v>
+        <v>16.70443718775948</v>
       </c>
       <c r="C6" t="n">
-        <v>181.8167295833966</v>
+        <v>210.4759085657695</v>
       </c>
       <c r="D6" t="n">
-        <v>50.87809302488671</v>
+        <v>66.41523219229674</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.282424543653592</v>
+        <v>5.809001166028376</v>
       </c>
       <c r="C7" t="n">
-        <v>148.5187926984575</v>
+        <v>108.6941970756856</v>
       </c>
       <c r="D7" t="n">
-        <v>35.33309987584271</v>
+        <v>37.90822410408209</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.422773407631881</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C8" t="n">
-        <v>92.54444734082557</v>
+        <v>55.15949476310704</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.331249886958674</v>
       </c>
       <c r="C9" t="n">
-        <v>33.17030968338697</v>
+        <v>33.61405964570653</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>26.95781021091316</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.281180754042088</v>
+        <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>25.62361508084176</v>
       </c>
       <c r="D10" t="n">
-        <v>23.91537407545231</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.7107853378746906</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>21.50125647070939</v>
+        <v>22.0343454741154</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>24.34439782220815</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.05550195525234</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="D12" t="n">
-        <v>21.69662426385451</v>
+        <v>20.61179305066178</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.78864650614645</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>26.11939767148639</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>8.296749848589794</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.541826921753</v>
+        <v>36.19212911705866</v>
       </c>
       <c r="D15" t="n">
-        <v>12.90016483380309</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0.4133157834879072</v>
       </c>
       <c r="D16" t="n">
-        <v>9.506263020221864</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31.03304493124168</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.955461500410399</v>
+        <v>0.3661918936840602</v>
       </c>
       <c r="C2" t="n">
-        <v>5.814891652253858</v>
+        <v>2.151990967709009</v>
       </c>
       <c r="D2" t="n">
-        <v>17.67538566725957</v>
+        <v>5.077599126364503</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.49965282819939</v>
+        <v>3.117048960983623</v>
       </c>
       <c r="C3" t="n">
-        <v>16.75843331149305</v>
+        <v>23.72884201164541</v>
       </c>
       <c r="D3" t="n">
-        <v>58.87540982368122</v>
+        <v>39.53988878854029</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>48.83016731382786</v>
+        <v>15.14934882423253</v>
       </c>
       <c r="C4" t="n">
-        <v>66.36614480708438</v>
+        <v>59.70400488606553</v>
       </c>
       <c r="D4" t="n">
-        <v>118.2721276783175</v>
+        <v>107.5514427479423</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>62.24280444924779</v>
+        <v>25.77087723647878</v>
       </c>
       <c r="C5" t="n">
-        <v>152.219981543468</v>
+        <v>124.3874341280709</v>
       </c>
       <c r="D5" t="n">
-        <v>112.72918014014</v>
+        <v>114.7908503190583</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.59633143376788</v>
+        <v>17.02645043475243</v>
       </c>
       <c r="C6" t="n">
-        <v>219.8545443844393</v>
+        <v>198.1186502124149</v>
       </c>
       <c r="D6" t="n">
-        <v>65.77120569831082</v>
+        <v>70.56115274733101</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.79872602509618</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>202.7760613213617</v>
+        <v>144.6261630511189</v>
       </c>
       <c r="D7" t="n">
-        <v>40.8426679920758</v>
+        <v>37.00992495469625</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.091744504851458</v>
+        <v>1.251728322914683</v>
       </c>
       <c r="C8" t="n">
-        <v>138.0239097400591</v>
+        <v>62.25262192629025</v>
       </c>
       <c r="D8" t="n">
-        <v>34.29735604786232</v>
+        <v>27.78836876870596</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.662499773917349</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>64.89843198923538</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>33.28124717396686</v>
+        <v>21.74374815365835</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.423534171157875</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>32.59893251951534</v>
+        <v>19.3600647277471</v>
       </c>
       <c r="D10" t="n">
-        <v>25.48126166372597</v>
+        <v>20.21418523044183</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>25.05518316008284</v>
+        <v>14.21570675749381</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="D12" t="n">
-        <v>22.34752299177014</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>16.1301147807751</v>
+        <v>13.78864650614645</v>
       </c>
       <c r="D13" t="n">
-        <v>16.3902779224005</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>14.13520344574558</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>14.74977750860408</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.61684065790326</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34.94432778496098</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.999239236474005</v>
+        <v>1.040652566501619</v>
       </c>
       <c r="C2" t="n">
-        <v>3.855323234577225</v>
+        <v>6.726935269499145</v>
       </c>
       <c r="D2" t="n">
-        <v>12.26301057374691</v>
+        <v>7.170685231818704</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.99267010218054</v>
+        <v>2.07148765596077</v>
       </c>
       <c r="C3" t="n">
-        <v>20.01292695107123</v>
+        <v>14.13225820263284</v>
       </c>
       <c r="D3" t="n">
-        <v>59.35155746024092</v>
+        <v>34.63115026730624</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.59745205019236</v>
+        <v>10.28675244509808</v>
       </c>
       <c r="C4" t="n">
-        <v>57.04935909378215</v>
+        <v>60.18898825196345</v>
       </c>
       <c r="D4" t="n">
-        <v>121.9477910830175</v>
+        <v>102.331490204462</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.86960145291376</v>
+        <v>24.98547907308133</v>
       </c>
       <c r="C5" t="n">
-        <v>145.445922384165</v>
+        <v>116.4598214162779</v>
       </c>
       <c r="D5" t="n">
-        <v>123.5774922720673</v>
+        <v>128.9525609528186</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>60.29698049943061</v>
+        <v>26.44533790929634</v>
       </c>
       <c r="C6" t="n">
-        <v>238.7325709894012</v>
+        <v>200.8960144677291</v>
       </c>
       <c r="D6" t="n">
-        <v>78.32972233103602</v>
+        <v>91.00899393138359</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>21.97838585497334</v>
+        <v>12.69596131131975</v>
       </c>
       <c r="C7" t="n">
-        <v>249.4876170894249</v>
+        <v>223.9160346369083</v>
       </c>
       <c r="D7" t="n">
-        <v>45.45393695892307</v>
+        <v>48.92736033654828</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.090361846519712</v>
+        <v>3.421390749300134</v>
       </c>
       <c r="C8" t="n">
-        <v>176.5771420858313</v>
+        <v>131.0142311317368</v>
       </c>
       <c r="D8" t="n">
-        <v>36.21667280966483</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>0.7765624340592268</v>
       </c>
       <c r="C9" t="n">
-        <v>79.87499321752047</v>
+        <v>55.1359328182051</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>23.74062298409636</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>33.73775985644164</v>
+        <v>28.32833000604172</v>
       </c>
       <c r="D10" t="n">
-        <v>25.90832191507333</v>
+        <v>20.92595231602077</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>24.87748682561417</v>
+        <v>18.48041878474196</v>
       </c>
       <c r="D11" t="n">
-        <v>24.52209415667683</v>
+        <v>18.65811511921063</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.44213062427633</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="D12" t="n">
-        <v>20.82875929330033</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.70734137314322</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>16.91060420565131</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>11.67690719431156</v>
+        <v>3.380157345721768</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3481,10 +3481,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.616578615996002</v>
+        <v>1.374446785945534</v>
       </c>
       <c r="C2" t="n">
-        <v>6.08487227092173</v>
+        <v>5.828636120113313</v>
       </c>
       <c r="D2" t="n">
-        <v>23.08088852684251</v>
+        <v>12.23061289950676</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.12596680577985</v>
+        <v>2.905973204570559</v>
       </c>
       <c r="C3" t="n">
-        <v>17.42602175038088</v>
+        <v>21.03394456348791</v>
       </c>
       <c r="D3" t="n">
-        <v>55.70927347748525</v>
+        <v>32.37803928605981</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.2288546927433</v>
+        <v>6.930157044278235</v>
       </c>
       <c r="C4" t="n">
-        <v>53.59066193172064</v>
+        <v>46.32867416340699</v>
       </c>
       <c r="D4" t="n">
-        <v>123.2113003783832</v>
+        <v>96.97114773927444</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>68.32964021557801</v>
+        <v>20.73942025221387</v>
       </c>
       <c r="C5" t="n">
-        <v>126.9645218517188</v>
+        <v>113.6618404591745</v>
       </c>
       <c r="D5" t="n">
-        <v>135.7757074973339</v>
+        <v>135.505726878666</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>73.41902031439348</v>
+        <v>30.67176177607885</v>
       </c>
       <c r="C6" t="n">
-        <v>236.4784782604505</v>
+        <v>193.77147137801</v>
       </c>
       <c r="D6" t="n">
-        <v>93.98761646606842</v>
+        <v>110.5310470303314</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.64493579289469</v>
+        <v>22.0382724649324</v>
       </c>
       <c r="C7" t="n">
-        <v>294.2828013387984</v>
+        <v>260.5067533218911</v>
       </c>
       <c r="D7" t="n">
-        <v>54.017722183068</v>
+        <v>62.82105384704915</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.18210635137117</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>240.1649408898972</v>
+        <v>216.0483085350743</v>
       </c>
       <c r="D8" t="n">
-        <v>38.97047512007713</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.884374755077128</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>135.2328010168853</v>
+        <v>108.7187407682918</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>25.84843530511426</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.8541205026947251</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>56.51430659496764</v>
+        <v>46.54956739686252</v>
       </c>
       <c r="D10" t="n">
-        <v>27.18950266911542</v>
+        <v>22.06477965294707</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>29.852984190737</v>
+        <v>25.41057582902019</v>
       </c>
       <c r="D11" t="n">
-        <v>25.05518316008284</v>
+        <v>19.36890045708532</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>17.35729941108361</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>15.4046032273367</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>14.04880964777186</v>
+        <v>15.08946221427348</v>
       </c>
       <c r="D13" t="n">
-        <v>17.17076734727672</v>
+        <v>9.626036240139976</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.98419422574081</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>11.98419422574081</v>
+        <v>3.994731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>9.316785713302231</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>1.239947350463722</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.068362486398782</v>
+        <v>6.363688618927824</v>
       </c>
       <c r="C2" t="n">
-        <v>5.775621744083985</v>
+        <v>3.451824928131785</v>
       </c>
       <c r="D2" t="n">
-        <v>5.396667130244716</v>
+        <v>11.10160303962293</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.927972564691488</v>
+        <v>1.150608309377262</v>
       </c>
       <c r="C2" t="n">
-        <v>3.358558896228339</v>
+        <v>6.42062998577414</v>
       </c>
       <c r="D2" t="n">
-        <v>16.98816227428681</v>
+        <v>10.67356104057132</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.49121800948867</v>
+        <v>3.799363615435157</v>
       </c>
       <c r="C3" t="n">
-        <v>22.0991408225957</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D3" t="n">
-        <v>63.59270754258714</v>
+        <v>34.11082398405542</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>51.48481310611123</v>
+        <v>6.177156555120932</v>
       </c>
       <c r="C4" t="n">
-        <v>76.10410028550849</v>
+        <v>49.45554060143307</v>
       </c>
       <c r="D4" t="n">
-        <v>127.4485234699124</v>
+        <v>90.99819470663685</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.49771469498668</v>
+        <v>16.32155558310323</v>
       </c>
       <c r="C5" t="n">
-        <v>195.5395989933585</v>
+        <v>98.6411005841983</v>
       </c>
       <c r="D5" t="n">
-        <v>126.57182277002</v>
+        <v>139.7026983143211</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.59376173908685</v>
+        <v>29.82647700272235</v>
       </c>
       <c r="C6" t="n">
-        <v>244.8105710263932</v>
+        <v>188.4180011467521</v>
       </c>
       <c r="D6" t="n">
-        <v>77.56494086942776</v>
+        <v>125.1021464567626</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.366053024963818</v>
+        <v>29.04500583014188</v>
       </c>
       <c r="C7" t="n">
-        <v>168.8802400845363</v>
+        <v>272.9032815834156</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>78.09213938660828</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>2.002765316663493</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="C8" t="n">
-        <v>99.63757450400877</v>
+        <v>277.1326506933108</v>
       </c>
       <c r="D8" t="n">
-        <v>25.11801501315464</v>
+        <v>43.72704274715294</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.5546874528994477</v>
+        <v>4.77031209493525</v>
       </c>
       <c r="C9" t="n">
-        <v>43.15468383557703</v>
+        <v>183.823421890877</v>
       </c>
       <c r="D9" t="n">
-        <v>20.74531073843935</v>
+        <v>28.39999758845172</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.9964739198105126</v>
       </c>
       <c r="C10" t="n">
+        <v>83.84616268119885</v>
+      </c>
+      <c r="D10" t="n">
         <v>23.34596040698915</v>
-      </c>
-      <c r="D10" t="n">
-        <v>19.64477156197868</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>17.41424077792992</v>
+        <v>37.84931924182727</v>
       </c>
       <c r="D11" t="n">
-        <v>17.05884810899257</v>
+        <v>20.07968579496001</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>11.28224461720434</v>
+        <v>22.1305567491316</v>
       </c>
       <c r="D12" t="n">
-        <v>13.88583952886689</v>
+        <v>16.05550195525234</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.886199381765381</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D13" t="n">
-        <v>9.886199381765381</v>
+        <v>10.40652566501619</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>16.59349969717959</v>
+        <v>16.90078672860884</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.609305471438775</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>25.083653843506</v>
+        <v>12.541826921753</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>0.7166758241001715</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.525676990128549</v>
+        <v>7.305184667300516</v>
       </c>
       <c r="C2" t="n">
-        <v>4.58279828342411</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="D2" t="n">
-        <v>20.59510333968959</v>
+        <v>19.92653315309751</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.6491972744144</v>
+        <v>10.49979169691964</v>
       </c>
       <c r="C3" t="n">
-        <v>14.78512042595696</v>
+        <v>6.813329067472864</v>
       </c>
       <c r="D3" t="n">
-        <v>7.883434065101888</v>
+        <v>10.59796646734432</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.197593330460869</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.26355035309465</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39938777827796</v>
+        <v>11.67831223053022</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14973601569048</v>
+        <v>59.94866945005516</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576398562150348</v>
+        <v>0.778554148702015</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.187554869240146</v>
+        <v>3.919136835353267</v>
       </c>
       <c r="C2" t="n">
-        <v>4.883213080923635</v>
+        <v>4.434554380082843</v>
       </c>
       <c r="D2" t="n">
-        <v>18.02783309308418</v>
+        <v>15.78159434576748</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.92042168269378</v>
+        <v>19.89020848804038</v>
       </c>
       <c r="C3" t="n">
-        <v>16.90078672860884</v>
+        <v>24.86276061005047</v>
       </c>
       <c r="D3" t="n">
-        <v>23.27723806769188</v>
+        <v>25.46653544816226</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.19741340401162</v>
+        <v>12.92863551722625</v>
       </c>
       <c r="C4" t="n">
-        <v>23.06223532046182</v>
+        <v>11.65236350170539</v>
       </c>
       <c r="D4" t="n">
-        <v>19.19513111343364</v>
+        <v>19.80774168088364</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>25.50089661781091</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.433973543006096</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.68556299720054</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>30.43025184083414</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.40326162673396</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.926230053461247</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.61179305066178</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.5156228333746</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>6.690610604442014</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.776546738526</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>24.6997904911455</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>23.65030219530566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44384257819353</v>
+        <v>13.62964407491056</v>
       </c>
       <c r="C21" t="n">
-        <v>86.16038490992183</v>
+        <v>73.76042675833948</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251335279619691</v>
+        <v>1.603487538224771</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.800165436690155</v>
+        <v>2.281581664669587</v>
       </c>
       <c r="C2" t="n">
-        <v>6.006332454581986</v>
+        <v>3.335978699030662</v>
       </c>
       <c r="D2" t="n">
-        <v>18.56877607812417</v>
+        <v>14.93336432929823</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.51928778228433</v>
+        <v>16.28228567493335</v>
       </c>
       <c r="C3" t="n">
-        <v>18.17215000560846</v>
+        <v>20.00310947402876</v>
       </c>
       <c r="D3" t="n">
-        <v>32.29459073119883</v>
+        <v>32.56948008838793</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.8835572382889</v>
+        <v>28.4098150654942</v>
       </c>
       <c r="C4" t="n">
-        <v>34.40829353844221</v>
+        <v>43.45706212848506</v>
       </c>
       <c r="D4" t="n">
-        <v>26.53369520267854</v>
+        <v>28.55020498720149</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.547496423800233</v>
+        <v>11.73188506574938</v>
       </c>
       <c r="C5" t="n">
-        <v>26.53173170727006</v>
+        <v>15.09437095279471</v>
       </c>
       <c r="D5" t="n">
-        <v>29.35425635697964</v>
+        <v>26.87534340375644</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>4.467933802027235</v>
       </c>
       <c r="C6" t="n">
-        <v>12.19625172985813</v>
+        <v>10.42517887139688</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>32.16107304342126</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>6.94684675525043</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.8823545064064</v>
       </c>
       <c r="D7" t="n">
-        <v>37.42913122440964</v>
+        <v>32.87774886752143</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>7.593818492349078</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>24.03318379996192</v>
       </c>
       <c r="D8" t="n">
-        <v>38.55323234577224</v>
+        <v>33.96356182841841</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.39843500367073</v>
+        <v>24.4062479275757</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.49843440078366</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.117670855789377</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.42408361716816</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>26.90381408717959</v>
       </c>
       <c r="D12" t="n">
-        <v>45.77987719673301</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.52854978444583</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.74107406778242</v>
+        <v>14.8421443396348</v>
       </c>
       <c r="C21" t="n">
-        <v>102.1205518134727</v>
+        <v>87.40373888896048</v>
       </c>
       <c r="D21" t="n">
-        <v>5.022322220334726</v>
+        <v>2.473690723272466</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.367214699117312</v>
+        <v>2.304161861867264</v>
       </c>
       <c r="C2" t="n">
-        <v>6.363688618927824</v>
+        <v>5.702972413969722</v>
       </c>
       <c r="D2" t="n">
-        <v>17.16978559957247</v>
+        <v>25.23484298996001</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.81519475189012</v>
+        <v>11.49626561673015</v>
       </c>
       <c r="C3" t="n">
-        <v>21.1910241961674</v>
+        <v>15.6834195753428</v>
       </c>
       <c r="D3" t="n">
-        <v>39.22082078466008</v>
+        <v>36.95789232637118</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.76717122984004</v>
+        <v>30.61776565234527</v>
       </c>
       <c r="C4" t="n">
-        <v>40.71307729511523</v>
+        <v>47.47731897737575</v>
       </c>
       <c r="D4" t="n">
-        <v>35.93981995706723</v>
+        <v>38.17329598422873</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.16295442337175</v>
+        <v>28.07798434145878</v>
       </c>
       <c r="C5" t="n">
-        <v>46.90299657039137</v>
+        <v>52.89165756629692</v>
       </c>
       <c r="D5" t="n">
-        <v>32.39767424014475</v>
+        <v>31.41592653589794</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.45913913041802</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="C6" t="n">
-        <v>27.85414586489051</v>
+        <v>17.99249017573129</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>33.85164259013428</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.407867265618931</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>17.54677671800324</v>
       </c>
       <c r="D7" t="n">
-        <v>39.46527596301753</v>
+        <v>34.85400699617026</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>25.86905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>40.38910055271378</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>28.06718511671205</v>
       </c>
       <c r="D9" t="n">
-        <v>41.93437143919824</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.45305302221006</v>
+        <v>27.75891633757857</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.12955930589413</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>6.75246070980956</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>27.8983245115816</v>
       </c>
       <c r="D11" t="n">
-        <v>50.46575898910303</v>
+        <v>45.66795795844887</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>34.71459882216721</v>
+        <v>29.07347651356504</v>
       </c>
       <c r="D12" t="n">
-        <v>47.29864089520282</v>
+        <v>43.39324852770902</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.04071898642641</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>46.30903920932205</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.80032966760617</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>37.77765165941727</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.67733346713483</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.07312835900488</v>
+        <v>16.08957958403864</v>
       </c>
       <c r="C21" t="n">
-        <v>117.905646913508</v>
+        <v>101.6183973728756</v>
       </c>
       <c r="D21" t="n">
-        <v>6.885001279620905</v>
+        <v>3.387279912429187</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.323837873681205</v>
+        <v>3.205406254365836</v>
       </c>
       <c r="C2" t="n">
-        <v>4.543528375254239</v>
+        <v>5.41433858892116</v>
       </c>
       <c r="D2" t="n">
-        <v>14.69283614175776</v>
+        <v>26.81349329838888</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.6062624173348</v>
+        <v>9.611310024576275</v>
       </c>
       <c r="C3" t="n">
-        <v>21.87824758914017</v>
+        <v>19.47296571373548</v>
       </c>
       <c r="D3" t="n">
-        <v>40.9683316982194</v>
+        <v>47.91419670576558</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.26193101505142</v>
+        <v>26.04871183678062</v>
       </c>
       <c r="C4" t="n">
-        <v>39.99836496642355</v>
+        <v>42.81892612072464</v>
       </c>
       <c r="D4" t="n">
-        <v>40.61097553387356</v>
+        <v>47.20930185411637</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.0521968592411</v>
+        <v>37.60093707265284</v>
       </c>
       <c r="C5" t="n">
-        <v>46.06851102178158</v>
+        <v>72.0602814917159</v>
       </c>
       <c r="D5" t="n">
-        <v>30.90050899116836</v>
+        <v>38.11635461738242</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.86794708601219</v>
+        <v>24.2717484920939</v>
       </c>
       <c r="C6" t="n">
-        <v>35.74347041621788</v>
+        <v>52.56866257159972</v>
       </c>
       <c r="D6" t="n">
-        <v>30.63151012020474</v>
+        <v>36.4277485660779</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>9.701630813366979</v>
       </c>
       <c r="C7" t="n">
-        <v>20.00212772632452</v>
+        <v>22.21793229480956</v>
       </c>
       <c r="D7" t="n">
-        <v>31.14103717870882</v>
+        <v>36.71049190490098</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="D8" t="n">
-        <v>30.37527396939631</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>22.18749811597791</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
-        <v>29.95312245657017</v>
+        <v>38.2734342500619</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.971791358484101</v>
       </c>
       <c r="C10" t="n">
-        <v>21.35301256736813</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>33.73775985644164</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.107853378746905</v>
       </c>
       <c r="C11" t="n">
-        <v>20.61277479836603</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>46.55643963079223</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>32.32797015314322</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.43908757017236</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.88498095434966</v>
       </c>
       <c r="D14" t="n">
-        <v>29.80684204863741</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.69215749368978</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.066861142933804</v>
+        <v>17.36513232156842</v>
       </c>
       <c r="C21" t="n">
-        <v>67.13518085787113</v>
+        <v>115.47812993843</v>
       </c>
       <c r="D21" t="n">
-        <v>5.300145857200353</v>
+        <v>4.341283080392105</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.812928156845365</v>
+        <v>3.928954312395735</v>
       </c>
       <c r="C2" t="n">
-        <v>3.814089830998858</v>
+        <v>8.319330045787471</v>
       </c>
       <c r="D2" t="n">
-        <v>16.25872373003143</v>
+        <v>21.9901668274243</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>22.32494279457247</v>
+        <v>10.26908098642164</v>
       </c>
       <c r="C3" t="n">
-        <v>19.16371518689774</v>
+        <v>20.29272504678157</v>
       </c>
       <c r="D3" t="n">
-        <v>43.60432428412209</v>
+        <v>57.01990666265475</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.77542612210151</v>
+        <v>22.21989579021806</v>
       </c>
       <c r="C4" t="n">
-        <v>49.69803228438204</v>
+        <v>45.97131799906114</v>
       </c>
       <c r="D4" t="n">
-        <v>53.28435664799564</v>
+        <v>58.68298727364885</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.74695543867836</v>
+        <v>38.48451000647497</v>
       </c>
       <c r="C5" t="n">
-        <v>63.76451339083034</v>
+        <v>75.69274799742909</v>
       </c>
       <c r="D5" t="n">
-        <v>39.17173339944774</v>
+        <v>46.04396732917541</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.60884780754905</v>
+        <v>37.35353665118265</v>
       </c>
       <c r="C6" t="n">
-        <v>58.56615929684348</v>
+        <v>82.99891441243386</v>
       </c>
       <c r="D6" t="n">
-        <v>34.21390749300134</v>
+        <v>39.80888765950392</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.761517423326035</v>
+        <v>18.80439552714341</v>
       </c>
       <c r="C7" t="n">
-        <v>39.16584291322225</v>
+        <v>49.0471335564664</v>
       </c>
       <c r="D7" t="n">
-        <v>33.59638818703009</v>
+        <v>39.22572952318131</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>9.262789589568655</v>
       </c>
       <c r="C8" t="n">
-        <v>23.699389580518</v>
+        <v>27.78836876870596</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.40781051235669</v>
+        <v>31.94999728700819</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>39.160934174701</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.398851609831464</v>
       </c>
       <c r="C10" t="n">
-        <v>24.91184799526281</v>
+        <v>34.59188035913637</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.45591614986479</v>
+        <v>34.11769621798515</v>
       </c>
       <c r="D11" t="n">
-        <v>34.82848155585983</v>
+        <v>47.26722496866692</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>33.41280136633594</v>
       </c>
       <c r="D12" t="n">
-        <v>33.41280136633594</v>
+        <v>44.69504598354028</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.33337761328319</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>31.21957699504857</v>
+        <v>43.1870815098172</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.91689560250429</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.9321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>26.86552592671396</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.294713244712785</v>
+        <v>18.66384067782199</v>
       </c>
       <c r="C21" t="n">
-        <v>77.50632822507333</v>
+        <v>128.8693761087709</v>
       </c>
       <c r="D21" t="n">
-        <v>6.382874089123686</v>
+        <v>5.33252590794914</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.360923302264331</v>
+        <v>3.457715414357266</v>
       </c>
       <c r="C2" t="n">
-        <v>9.127308406382596</v>
+        <v>5.057964172279567</v>
       </c>
       <c r="D2" t="n">
-        <v>20.98289368286708</v>
+        <v>17.17371259038945</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.1762979806037</v>
+        <v>14.45132620651305</v>
       </c>
       <c r="C3" t="n">
-        <v>16.47863521578271</v>
+        <v>33.06526267903257</v>
       </c>
       <c r="D3" t="n">
-        <v>46.72628198362694</v>
+        <v>63.11165116750621</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>38.14777054391831</v>
+        <v>18.48041878474196</v>
       </c>
       <c r="C4" t="n">
-        <v>48.72806555258618</v>
+        <v>67.34887425903544</v>
       </c>
       <c r="D4" t="n">
-        <v>63.77531261557705</v>
+        <v>55.84966339919255</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.4599663138688</v>
+        <v>21.03394456348791</v>
       </c>
       <c r="C5" t="n">
-        <v>80.45422436302613</v>
+        <v>49.57825906446394</v>
       </c>
       <c r="D5" t="n">
-        <v>50.11822030179968</v>
+        <v>37.47821860962199</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.43654323768712</v>
+        <v>11.67298020349458</v>
       </c>
       <c r="C6" t="n">
-        <v>83.03916606830798</v>
+        <v>32.28182801104362</v>
       </c>
       <c r="D6" t="n">
-        <v>38.84284791852506</v>
+        <v>25.80131141531043</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.02586959767568</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>64.97697180557515</v>
+        <v>19.52303484665207</v>
       </c>
       <c r="D7" t="n">
-        <v>36.47094546506476</v>
+        <v>27.48795397120644</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.344855486097888</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>39.47116644924301</v>
+        <v>23.53249247079604</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>28.78975142703771</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.657812019574366</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>27.5124976638126</v>
+        <v>26.40312275801371</v>
       </c>
       <c r="D9" t="n">
-        <v>32.72655972106742</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>37.01188845010476</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>27.00984283923824</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>25.16808414607123</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>23.41468274628643</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>34.60169783617884</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>24.58296251434014</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>24.36697801940583</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>25.21226279276234</v>
       </c>
       <c r="D16" t="n">
-        <v>27.27884171020187</v>
+        <v>30.58536797810513</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.9165768073348</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>25.97213551584937</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
-        <v>21.40209995258047</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.85071759569225</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>97.51209072431442</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.511747602117198</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>87.32406587461242</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.511747602117198</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
